--- a/docs/original/00_공정도_WBS.xlsx
+++ b/docs/original/00_공정도_WBS.xlsx
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG154"/>
+  <dimension ref="A1:BG162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>[범례] 회색 막대 = 원래 계획 일정 (수정하지 않음)  /  파란 막대 = 실제 진행 일정 (1.0~2.0 계획대로, 3.0 구현은 AI 활용)</t>
+          <t>[범례] 회색 막대 = 계획 일정  /  파란 막대 = 실제 진행 일정</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       <c r="B34" s="17" t="n"/>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [회원가입·로그인] 매장 등록 및 회원가입 (입력, 유효성검사, 가입승인대기)</t>
+          <t>↳ 실제 진행: [회원가입·로그인] 매장 등록 및 회원가입 (입력, 유효성검사, 가입승인대기)</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
@@ -3218,11 +3218,11 @@
         <v>46265</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G34" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 2일 단축 완료</t>
+          <t>계획 대비 1일 단축 완료</t>
         </is>
       </c>
       <c r="H34" s="16" t="n"/>
@@ -3241,7 +3241,7 @@
       <c r="U34" s="16" t="n"/>
       <c r="V34" s="21" t="n"/>
       <c r="W34" s="21" t="n"/>
-      <c r="X34" s="16" t="n"/>
+      <c r="X34" s="21" t="n"/>
       <c r="Y34" s="16" t="n"/>
       <c r="Z34" s="16" t="n"/>
       <c r="AA34" s="16" t="n"/>
@@ -3358,7 +3358,7 @@
       <c r="B36" s="17" t="n"/>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [회원가입·로그인] 로그인 · 로그아웃 (세션생성, 권한별 리다이렉트)</t>
+          <t>↳ 실제 진행: [회원가입·로그인] 로그인 · 로그아웃 (세션생성, 권한별 리다이렉트)</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
@@ -3367,14 +3367,14 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="G36" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 2일 단축 완료</t>
+          <t>계획 대비 1일 단축 완료</t>
         </is>
       </c>
       <c r="H36" s="16" t="n"/>
@@ -3393,9 +3393,9 @@
       <c r="U36" s="16" t="n"/>
       <c r="V36" s="16" t="n"/>
       <c r="W36" s="16" t="n"/>
-      <c r="X36" s="21" t="n"/>
-      <c r="Y36" s="16" t="n"/>
-      <c r="Z36" s="16" t="n"/>
+      <c r="X36" s="16" t="n"/>
+      <c r="Y36" s="21" t="n"/>
+      <c r="Z36" s="21" t="n"/>
       <c r="AA36" s="16" t="n"/>
       <c r="AB36" s="16" t="n"/>
       <c r="AC36" s="16" t="n"/>
@@ -3510,7 +3510,7 @@
       <c r="B38" s="17" t="n"/>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [직원관리] 가입승인 (목록, 승인/거절)</t>
+          <t>↳ 실제 진행: [직원관리] 가입승인 (목록, 승인/거절)</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
@@ -3519,14 +3519,14 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>46268</v>
+        <v>46271</v>
       </c>
       <c r="G38" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 1일 단축 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H38" s="16" t="n"/>
@@ -3546,10 +3546,10 @@
       <c r="V38" s="16" t="n"/>
       <c r="W38" s="16" t="n"/>
       <c r="X38" s="16" t="n"/>
-      <c r="Y38" s="21" t="n"/>
+      <c r="Y38" s="16" t="n"/>
       <c r="Z38" s="16" t="n"/>
-      <c r="AA38" s="16" t="n"/>
-      <c r="AB38" s="16" t="n"/>
+      <c r="AA38" s="21" t="n"/>
+      <c r="AB38" s="21" t="n"/>
       <c r="AC38" s="16" t="n"/>
       <c r="AD38" s="16" t="n"/>
       <c r="AE38" s="16" t="n"/>
@@ -3662,7 +3662,7 @@
       <c r="B40" s="22" t="n"/>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [직원관리] 근태관리 (퇴직/복직 처리)</t>
+          <t>↳ 실제 진행: [직원관리] 근태관리 (퇴직/복직 처리)</t>
         </is>
       </c>
       <c r="D40" s="19" t="inlineStr">
@@ -3671,14 +3671,14 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="G40" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 1일 단축 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H40" s="16" t="n"/>
@@ -3699,11 +3699,11 @@
       <c r="W40" s="16" t="n"/>
       <c r="X40" s="16" t="n"/>
       <c r="Y40" s="16" t="n"/>
-      <c r="Z40" s="21" t="n"/>
+      <c r="Z40" s="16" t="n"/>
       <c r="AA40" s="16" t="n"/>
       <c r="AB40" s="16" t="n"/>
-      <c r="AC40" s="16" t="n"/>
-      <c r="AD40" s="16" t="n"/>
+      <c r="AC40" s="21" t="n"/>
+      <c r="AD40" s="21" t="n"/>
       <c r="AE40" s="16" t="n"/>
       <c r="AF40" s="16" t="n"/>
       <c r="AG40" s="16" t="n"/>
@@ -3818,7 +3818,7 @@
       <c r="B42" s="17" t="n"/>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [일보] 작성 (등록)</t>
+          <t>↳ 실제 진행: [일보] 작성 (등록)</t>
         </is>
       </c>
       <c r="D42" s="19" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="G42" s="18" t="inlineStr">
         <is>
-          <t>AI 활용, 계획대로 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H42" s="16" t="n"/>
@@ -3970,7 +3970,7 @@
       <c r="B44" s="17" t="n"/>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [일보] 조회 (목록, 상세보기)</t>
+          <t>↳ 실제 진행: [일보] 조회 (목록, 상세보기)</t>
         </is>
       </c>
       <c r="D44" s="19" t="inlineStr">
@@ -3982,11 +3982,11 @@
         <v>46266</v>
       </c>
       <c r="F44" s="20" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G44" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 1일 단축 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H44" s="16" t="n"/>
@@ -4005,7 +4005,7 @@
       <c r="U44" s="16" t="n"/>
       <c r="V44" s="16" t="n"/>
       <c r="W44" s="21" t="n"/>
-      <c r="X44" s="16" t="n"/>
+      <c r="X44" s="21" t="n"/>
       <c r="Y44" s="16" t="n"/>
       <c r="Z44" s="16" t="n"/>
       <c r="AA44" s="16" t="n"/>
@@ -4122,7 +4122,7 @@
       <c r="B46" s="17" t="n"/>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [일보] 수정 · 삭제</t>
+          <t>↳ 실제 진행: [일보] 수정 · 삭제</t>
         </is>
       </c>
       <c r="D46" s="19" t="inlineStr">
@@ -4131,14 +4131,14 @@
         </is>
       </c>
       <c r="E46" s="20" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F46" s="20" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="G46" s="18" t="inlineStr">
         <is>
-          <t>AI 활용, 계획대로 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H46" s="16" t="n"/>
@@ -4157,8 +4157,8 @@
       <c r="U46" s="16" t="n"/>
       <c r="V46" s="16" t="n"/>
       <c r="W46" s="16" t="n"/>
-      <c r="X46" s="21" t="n"/>
-      <c r="Y46" s="16" t="n"/>
+      <c r="X46" s="16" t="n"/>
+      <c r="Y46" s="21" t="n"/>
       <c r="Z46" s="16" t="n"/>
       <c r="AA46" s="16" t="n"/>
       <c r="AB46" s="16" t="n"/>
@@ -4274,7 +4274,7 @@
       <c r="B48" s="17" t="n"/>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [일보] 댓글 (등록/삭제)</t>
+          <t>↳ 실제 진행: [일보] 댓글 (등록/삭제)</t>
         </is>
       </c>
       <c r="D48" s="19" t="inlineStr">
@@ -4283,14 +4283,14 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F48" s="20" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="G48" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 1일 단축 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H48" s="16" t="n"/>
@@ -4310,9 +4310,9 @@
       <c r="V48" s="16" t="n"/>
       <c r="W48" s="16" t="n"/>
       <c r="X48" s="16" t="n"/>
-      <c r="Y48" s="21" t="n"/>
-      <c r="Z48" s="16" t="n"/>
-      <c r="AA48" s="16" t="n"/>
+      <c r="Y48" s="16" t="n"/>
+      <c r="Z48" s="21" t="n"/>
+      <c r="AA48" s="21" t="n"/>
       <c r="AB48" s="16" t="n"/>
       <c r="AC48" s="16" t="n"/>
       <c r="AD48" s="16" t="n"/>
@@ -4426,7 +4426,7 @@
       <c r="B50" s="17" t="n"/>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [공지사항] 등록 (사장 전용)</t>
+          <t>↳ 실제 진행: [공지사항] 등록 (사장 전용)</t>
         </is>
       </c>
       <c r="D50" s="19" t="inlineStr">
@@ -4435,14 +4435,14 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>46269</v>
+        <v>46271</v>
       </c>
       <c r="F50" s="20" t="n">
-        <v>46269</v>
+        <v>46271</v>
       </c>
       <c r="G50" s="18" t="inlineStr">
         <is>
-          <t>AI 활용, 계획대로 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H50" s="16" t="n"/>
@@ -4463,9 +4463,9 @@
       <c r="W50" s="16" t="n"/>
       <c r="X50" s="16" t="n"/>
       <c r="Y50" s="16" t="n"/>
-      <c r="Z50" s="21" t="n"/>
+      <c r="Z50" s="16" t="n"/>
       <c r="AA50" s="16" t="n"/>
-      <c r="AB50" s="16" t="n"/>
+      <c r="AB50" s="21" t="n"/>
       <c r="AC50" s="16" t="n"/>
       <c r="AD50" s="16" t="n"/>
       <c r="AE50" s="16" t="n"/>
@@ -4578,7 +4578,7 @@
       <c r="B52" s="17" t="n"/>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [공지사항] 조회 (목록, 상세보기·읽음처리)</t>
+          <t>↳ 실제 진행: [공지사항] 조회 (목록, 상세보기·읽음처리)</t>
         </is>
       </c>
       <c r="D52" s="19" t="inlineStr">
@@ -4587,14 +4587,14 @@
         </is>
       </c>
       <c r="E52" s="20" t="n">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="F52" s="20" t="n">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="G52" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 1일 단축 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H52" s="16" t="n"/>
@@ -4616,10 +4616,10 @@
       <c r="X52" s="16" t="n"/>
       <c r="Y52" s="16" t="n"/>
       <c r="Z52" s="16" t="n"/>
-      <c r="AA52" s="21" t="n"/>
+      <c r="AA52" s="16" t="n"/>
       <c r="AB52" s="16" t="n"/>
-      <c r="AC52" s="16" t="n"/>
-      <c r="AD52" s="16" t="n"/>
+      <c r="AC52" s="21" t="n"/>
+      <c r="AD52" s="21" t="n"/>
       <c r="AE52" s="16" t="n"/>
       <c r="AF52" s="16" t="n"/>
       <c r="AG52" s="16" t="n"/>
@@ -4730,7 +4730,7 @@
       <c r="B54" s="17" t="n"/>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [공지사항] 수정</t>
+          <t>↳ 실제 진행: [공지사항] 수정</t>
         </is>
       </c>
       <c r="D54" s="19" t="inlineStr">
@@ -4739,14 +4739,14 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>46271</v>
+        <v>46274</v>
       </c>
       <c r="F54" s="20" t="n">
-        <v>46271</v>
+        <v>46274</v>
       </c>
       <c r="G54" s="18" t="inlineStr">
         <is>
-          <t>AI 활용, 계획대로 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H54" s="16" t="n"/>
@@ -4769,10 +4769,10 @@
       <c r="Y54" s="16" t="n"/>
       <c r="Z54" s="16" t="n"/>
       <c r="AA54" s="16" t="n"/>
-      <c r="AB54" s="21" t="n"/>
+      <c r="AB54" s="16" t="n"/>
       <c r="AC54" s="16" t="n"/>
       <c r="AD54" s="16" t="n"/>
-      <c r="AE54" s="16" t="n"/>
+      <c r="AE54" s="21" t="n"/>
       <c r="AF54" s="16" t="n"/>
       <c r="AG54" s="16" t="n"/>
       <c r="AH54" s="16" t="n"/>
@@ -4882,7 +4882,7 @@
       <c r="B56" s="17" t="n"/>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [출퇴근관리] 출근 / 퇴근 등록</t>
+          <t>↳ 실제 진행: [출퇴근관리] 출근 / 퇴근 등록</t>
         </is>
       </c>
       <c r="D56" s="19" t="inlineStr">
@@ -4891,14 +4891,14 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="F56" s="20" t="n">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="G56" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 1일 단축 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H56" s="16" t="n"/>
@@ -4922,11 +4922,11 @@
       <c r="Z56" s="16" t="n"/>
       <c r="AA56" s="16" t="n"/>
       <c r="AB56" s="16" t="n"/>
-      <c r="AC56" s="21" t="n"/>
+      <c r="AC56" s="16" t="n"/>
       <c r="AD56" s="16" t="n"/>
       <c r="AE56" s="16" t="n"/>
-      <c r="AF56" s="16" t="n"/>
-      <c r="AG56" s="16" t="n"/>
+      <c r="AF56" s="21" t="n"/>
+      <c r="AG56" s="21" t="n"/>
       <c r="AH56" s="16" t="n"/>
       <c r="AI56" s="16" t="n"/>
       <c r="AJ56" s="16" t="n"/>
@@ -5034,7 +5034,7 @@
       <c r="B58" s="22" t="n"/>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [출퇴근관리] 휴게관리 (시작·종료)</t>
+          <t>↳ 실제 진행: [출퇴근관리] 휴게관리 (시작·종료)</t>
         </is>
       </c>
       <c r="D58" s="19" t="inlineStr">
@@ -5043,14 +5043,14 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>46273</v>
+        <v>46277</v>
       </c>
       <c r="F58" s="20" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="G58" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 1일 단축 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H58" s="16" t="n"/>
@@ -5075,12 +5075,12 @@
       <c r="AA58" s="16" t="n"/>
       <c r="AB58" s="16" t="n"/>
       <c r="AC58" s="16" t="n"/>
-      <c r="AD58" s="21" t="n"/>
+      <c r="AD58" s="16" t="n"/>
       <c r="AE58" s="16" t="n"/>
       <c r="AF58" s="16" t="n"/>
       <c r="AG58" s="16" t="n"/>
-      <c r="AH58" s="16" t="n"/>
-      <c r="AI58" s="16" t="n"/>
+      <c r="AH58" s="21" t="n"/>
+      <c r="AI58" s="21" t="n"/>
       <c r="AJ58" s="16" t="n"/>
       <c r="AK58" s="16" t="n"/>
       <c r="AL58" s="16" t="n"/>
@@ -5190,7 +5190,7 @@
       <c r="B60" s="17" t="n"/>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [재고관리] 목록 (조회, 재고부족 하이라이트)</t>
+          <t>↳ 실제 진행: [재고관리] 목록 (조회, 재고부족 하이라이트)</t>
         </is>
       </c>
       <c r="D60" s="19" t="inlineStr">
@@ -5202,11 +5202,11 @@
         <v>46265</v>
       </c>
       <c r="F60" s="20" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G60" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 2일 단축 완료</t>
+          <t>계획 대비 1일 단축 완료</t>
         </is>
       </c>
       <c r="H60" s="16" t="n"/>
@@ -5224,7 +5224,7 @@
       <c r="T60" s="16" t="n"/>
       <c r="U60" s="16" t="n"/>
       <c r="V60" s="21" t="n"/>
-      <c r="W60" s="16" t="n"/>
+      <c r="W60" s="21" t="n"/>
       <c r="X60" s="16" t="n"/>
       <c r="Y60" s="16" t="n"/>
       <c r="Z60" s="16" t="n"/>
@@ -5342,7 +5342,7 @@
       <c r="B62" s="17" t="n"/>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [재고관리] 입고 (등록)</t>
+          <t>↳ 실제 진행: [재고관리] 입고 (등록)</t>
         </is>
       </c>
       <c r="D62" s="19" t="inlineStr">
@@ -5351,14 +5351,14 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F62" s="20" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="G62" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 2일 단축 완료</t>
+          <t>계획 대비 1일 단축 완료</t>
         </is>
       </c>
       <c r="H62" s="16" t="n"/>
@@ -5376,9 +5376,9 @@
       <c r="T62" s="16" t="n"/>
       <c r="U62" s="16" t="n"/>
       <c r="V62" s="16" t="n"/>
-      <c r="W62" s="21" t="n"/>
-      <c r="X62" s="16" t="n"/>
-      <c r="Y62" s="16" t="n"/>
+      <c r="W62" s="16" t="n"/>
+      <c r="X62" s="21" t="n"/>
+      <c r="Y62" s="21" t="n"/>
       <c r="Z62" s="16" t="n"/>
       <c r="AA62" s="16" t="n"/>
       <c r="AB62" s="16" t="n"/>
@@ -5494,7 +5494,7 @@
       <c r="B64" s="17" t="n"/>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [재고관리] 폐기 (등록)</t>
+          <t>↳ 실제 진행: [재고관리] 폐기 (등록)</t>
         </is>
       </c>
       <c r="D64" s="19" t="inlineStr">
@@ -5503,14 +5503,14 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="F64" s="20" t="n">
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="G64" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 1일 단축 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H64" s="16" t="n"/>
@@ -5529,10 +5529,10 @@
       <c r="U64" s="16" t="n"/>
       <c r="V64" s="16" t="n"/>
       <c r="W64" s="16" t="n"/>
-      <c r="X64" s="21" t="n"/>
+      <c r="X64" s="16" t="n"/>
       <c r="Y64" s="16" t="n"/>
-      <c r="Z64" s="16" t="n"/>
-      <c r="AA64" s="16" t="n"/>
+      <c r="Z64" s="21" t="n"/>
+      <c r="AA64" s="21" t="n"/>
       <c r="AB64" s="16" t="n"/>
       <c r="AC64" s="16" t="n"/>
       <c r="AD64" s="16" t="n"/>
@@ -5646,7 +5646,7 @@
       <c r="B66" s="17" t="n"/>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [AI 재고실사] 사진 촬영 / 업로드 (이미지 첨부)</t>
+          <t>↳ 실제 진행: [AI 재고실사] 사진 촬영 / 업로드 (이미지 첨부)</t>
         </is>
       </c>
       <c r="D66" s="19" t="inlineStr">
@@ -5655,14 +5655,14 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>46268</v>
+        <v>46271</v>
       </c>
       <c r="F66" s="20" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="G66" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 1일 단축 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H66" s="16" t="n"/>
@@ -5682,11 +5682,11 @@
       <c r="V66" s="16" t="n"/>
       <c r="W66" s="16" t="n"/>
       <c r="X66" s="16" t="n"/>
-      <c r="Y66" s="21" t="n"/>
+      <c r="Y66" s="16" t="n"/>
       <c r="Z66" s="16" t="n"/>
       <c r="AA66" s="16" t="n"/>
-      <c r="AB66" s="16" t="n"/>
-      <c r="AC66" s="16" t="n"/>
+      <c r="AB66" s="21" t="n"/>
+      <c r="AC66" s="21" t="n"/>
       <c r="AD66" s="16" t="n"/>
       <c r="AE66" s="16" t="n"/>
       <c r="AF66" s="16" t="n"/>
@@ -5798,7 +5798,7 @@
       <c r="B68" s="17" t="n"/>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [AI 재고실사] AI 인식결과 검토 (Gemini Vision 연동)</t>
+          <t>↳ 실제 진행: [AI 재고실사] AI 인식결과 검토 (Gemini Vision 연동)</t>
         </is>
       </c>
       <c r="D68" s="19" t="inlineStr">
@@ -5807,14 +5807,14 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="F68" s="20" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="G68" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 2일 단축 완료</t>
+          <t>계획 대비 1일 단축 완료</t>
         </is>
       </c>
       <c r="H68" s="16" t="n"/>
@@ -5835,12 +5835,12 @@
       <c r="W68" s="16" t="n"/>
       <c r="X68" s="16" t="n"/>
       <c r="Y68" s="16" t="n"/>
-      <c r="Z68" s="21" t="n"/>
+      <c r="Z68" s="16" t="n"/>
       <c r="AA68" s="16" t="n"/>
       <c r="AB68" s="16" t="n"/>
       <c r="AC68" s="16" t="n"/>
-      <c r="AD68" s="16" t="n"/>
-      <c r="AE68" s="16" t="n"/>
+      <c r="AD68" s="21" t="n"/>
+      <c r="AE68" s="21" t="n"/>
       <c r="AF68" s="16" t="n"/>
       <c r="AG68" s="16" t="n"/>
       <c r="AH68" s="16" t="n"/>
@@ -5950,7 +5950,7 @@
       <c r="B70" s="17" t="n"/>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [AI 재고실사] 보정 (수동 수정)</t>
+          <t>↳ 실제 진행: [AI 재고실사] 보정 (수동 수정)</t>
         </is>
       </c>
       <c r="D70" s="19" t="inlineStr">
@@ -5959,14 +5959,14 @@
         </is>
       </c>
       <c r="E70" s="20" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="F70" s="20" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="G70" s="18" t="inlineStr">
         <is>
-          <t>AI 활용, 계획대로 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H70" s="16" t="n"/>
@@ -5988,12 +5988,12 @@
       <c r="X70" s="16" t="n"/>
       <c r="Y70" s="16" t="n"/>
       <c r="Z70" s="16" t="n"/>
-      <c r="AA70" s="21" t="n"/>
+      <c r="AA70" s="16" t="n"/>
       <c r="AB70" s="16" t="n"/>
       <c r="AC70" s="16" t="n"/>
       <c r="AD70" s="16" t="n"/>
       <c r="AE70" s="16" t="n"/>
-      <c r="AF70" s="16" t="n"/>
+      <c r="AF70" s="21" t="n"/>
       <c r="AG70" s="16" t="n"/>
       <c r="AH70" s="16" t="n"/>
       <c r="AI70" s="16" t="n"/>
@@ -6102,7 +6102,7 @@
       <c r="B72" s="22" t="n"/>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [AI 재고실사] 확정 반영 (재고 데이터 갱신)</t>
+          <t>↳ 실제 진행: [AI 재고실사] 확정 반영 (재고 데이터 갱신)</t>
         </is>
       </c>
       <c r="D72" s="19" t="inlineStr">
@@ -6111,14 +6111,14 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="F72" s="20" t="n">
-        <v>46271</v>
+        <v>46277</v>
       </c>
       <c r="G72" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 1일 단축 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H72" s="16" t="n"/>
@@ -6141,13 +6141,13 @@
       <c r="Y72" s="16" t="n"/>
       <c r="Z72" s="16" t="n"/>
       <c r="AA72" s="16" t="n"/>
-      <c r="AB72" s="21" t="n"/>
+      <c r="AB72" s="16" t="n"/>
       <c r="AC72" s="16" t="n"/>
       <c r="AD72" s="16" t="n"/>
       <c r="AE72" s="16" t="n"/>
       <c r="AF72" s="16" t="n"/>
-      <c r="AG72" s="16" t="n"/>
-      <c r="AH72" s="16" t="n"/>
+      <c r="AG72" s="21" t="n"/>
+      <c r="AH72" s="21" t="n"/>
       <c r="AI72" s="16" t="n"/>
       <c r="AJ72" s="16" t="n"/>
       <c r="AK72" s="16" t="n"/>
@@ -6258,7 +6258,7 @@
       <c r="B74" s="17" t="n"/>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [예약관리] 예약접수 (등록, 중복확인)</t>
+          <t>↳ 실제 진행: [예약관리] 예약접수 (등록, 중복확인)</t>
         </is>
       </c>
       <c r="D74" s="19" t="inlineStr">
@@ -6270,11 +6270,11 @@
         <v>46265</v>
       </c>
       <c r="F74" s="20" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G74" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 3일 단축 완료</t>
+          <t>계획 대비 2일 단축 완료</t>
         </is>
       </c>
       <c r="H74" s="16" t="n"/>
@@ -6293,7 +6293,7 @@
       <c r="U74" s="16" t="n"/>
       <c r="V74" s="21" t="n"/>
       <c r="W74" s="21" t="n"/>
-      <c r="X74" s="16" t="n"/>
+      <c r="X74" s="21" t="n"/>
       <c r="Y74" s="16" t="n"/>
       <c r="Z74" s="16" t="n"/>
       <c r="AA74" s="16" t="n"/>
@@ -6410,7 +6410,7 @@
       <c r="B76" s="22" t="n"/>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [예약관리] 예약조회 (목록, 수정·취소)</t>
+          <t>↳ 실제 진행: [예약관리] 예약조회 (목록, 수정·취소)</t>
         </is>
       </c>
       <c r="D76" s="19" t="inlineStr">
@@ -6419,14 +6419,14 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F76" s="20" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="G76" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 3일 단축 완료</t>
+          <t>계획 대비 2일 단축 완료</t>
         </is>
       </c>
       <c r="H76" s="16" t="n"/>
@@ -6445,10 +6445,10 @@
       <c r="U76" s="16" t="n"/>
       <c r="V76" s="16" t="n"/>
       <c r="W76" s="16" t="n"/>
-      <c r="X76" s="21" t="n"/>
+      <c r="X76" s="16" t="n"/>
       <c r="Y76" s="21" t="n"/>
-      <c r="Z76" s="16" t="n"/>
-      <c r="AA76" s="16" t="n"/>
+      <c r="Z76" s="21" t="n"/>
+      <c r="AA76" s="21" t="n"/>
       <c r="AB76" s="16" t="n"/>
       <c r="AC76" s="16" t="n"/>
       <c r="AD76" s="16" t="n"/>
@@ -6566,7 +6566,7 @@
       <c r="B78" s="17" t="n"/>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [관리자 대시보드] 예약 현황 요약 UI</t>
+          <t>↳ 실제 진행: [관리자 대시보드] 예약 현황 요약 UI</t>
         </is>
       </c>
       <c r="D78" s="19" t="inlineStr">
@@ -6578,11 +6578,11 @@
         <v>46265</v>
       </c>
       <c r="F78" s="20" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G78" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 2일 단축 완료</t>
+          <t>계획 대비 1일 단축 완료</t>
         </is>
       </c>
       <c r="H78" s="16" t="n"/>
@@ -6600,7 +6600,7 @@
       <c r="T78" s="16" t="n"/>
       <c r="U78" s="16" t="n"/>
       <c r="V78" s="21" t="n"/>
-      <c r="W78" s="16" t="n"/>
+      <c r="W78" s="21" t="n"/>
       <c r="X78" s="16" t="n"/>
       <c r="Y78" s="16" t="n"/>
       <c r="Z78" s="16" t="n"/>
@@ -6718,7 +6718,7 @@
       <c r="B80" s="17" t="n"/>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [관리자 대시보드] 재고 현황 요약 UI</t>
+          <t>↳ 실제 진행: [관리자 대시보드] 재고 현황 요약 UI</t>
         </is>
       </c>
       <c r="D80" s="19" t="inlineStr">
@@ -6727,14 +6727,14 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F80" s="20" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="G80" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 1일 단축 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H80" s="16" t="n"/>
@@ -6752,9 +6752,9 @@
       <c r="T80" s="16" t="n"/>
       <c r="U80" s="16" t="n"/>
       <c r="V80" s="16" t="n"/>
-      <c r="W80" s="21" t="n"/>
-      <c r="X80" s="16" t="n"/>
-      <c r="Y80" s="16" t="n"/>
+      <c r="W80" s="16" t="n"/>
+      <c r="X80" s="21" t="n"/>
+      <c r="Y80" s="21" t="n"/>
       <c r="Z80" s="16" t="n"/>
       <c r="AA80" s="16" t="n"/>
       <c r="AB80" s="16" t="n"/>
@@ -6870,7 +6870,7 @@
       <c r="B82" s="17" t="n"/>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [관리자 대시보드] 실시간 갱신 로직</t>
+          <t>↳ 실제 진행: [관리자 대시보드] 실시간 갱신 로직</t>
         </is>
       </c>
       <c r="D82" s="19" t="inlineStr">
@@ -6879,14 +6879,14 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="F82" s="20" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="G82" s="18" t="inlineStr">
         <is>
-          <t>AI 활용, 계획대로 완료</t>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H82" s="16" t="n"/>
@@ -6905,9 +6905,9 @@
       <c r="U82" s="16" t="n"/>
       <c r="V82" s="16" t="n"/>
       <c r="W82" s="16" t="n"/>
-      <c r="X82" s="21" t="n"/>
+      <c r="X82" s="16" t="n"/>
       <c r="Y82" s="16" t="n"/>
-      <c r="Z82" s="16" t="n"/>
+      <c r="Z82" s="21" t="n"/>
       <c r="AA82" s="16" t="n"/>
       <c r="AB82" s="16" t="n"/>
       <c r="AC82" s="16" t="n"/>
@@ -7022,7 +7022,7 @@
       <c r="B84" s="17" t="n"/>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: 알림 (통합 알림)</t>
+          <t>↳ 실제 진행: 알림 (통합 알림)</t>
         </is>
       </c>
       <c r="D84" s="19" t="inlineStr">
@@ -7031,14 +7031,14 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="F84" s="20" t="n">
-        <v>46268</v>
+        <v>46271</v>
       </c>
       <c r="G84" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 2일 단축 완료</t>
+          <t>계획 대비 1일 단축 완료</t>
         </is>
       </c>
       <c r="H84" s="16" t="n"/>
@@ -7058,10 +7058,10 @@
       <c r="V84" s="16" t="n"/>
       <c r="W84" s="16" t="n"/>
       <c r="X84" s="16" t="n"/>
-      <c r="Y84" s="21" t="n"/>
+      <c r="Y84" s="16" t="n"/>
       <c r="Z84" s="16" t="n"/>
-      <c r="AA84" s="16" t="n"/>
-      <c r="AB84" s="16" t="n"/>
+      <c r="AA84" s="21" t="n"/>
+      <c r="AB84" s="21" t="n"/>
       <c r="AC84" s="16" t="n"/>
       <c r="AD84" s="16" t="n"/>
       <c r="AE84" s="16" t="n"/>
@@ -7174,7 +7174,7 @@
       <c r="B86" s="17" t="n"/>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [전체 일정관리] 통합 캘린더 조회 (공지·예약·근무스케줄 통합표시)</t>
+          <t>↳ 실제 진행: [전체 일정관리] 통합 캘린더 조회 (공지·예약·근무스케줄 통합표시)</t>
         </is>
       </c>
       <c r="D86" s="19" t="inlineStr">
@@ -7183,14 +7183,14 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="F86" s="20" t="n">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="G86" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 2일 단축 완료</t>
+          <t>계획 대비 1일 단축 완료</t>
         </is>
       </c>
       <c r="H86" s="16" t="n"/>
@@ -7211,12 +7211,12 @@
       <c r="W86" s="16" t="n"/>
       <c r="X86" s="16" t="n"/>
       <c r="Y86" s="16" t="n"/>
-      <c r="Z86" s="21" t="n"/>
-      <c r="AA86" s="21" t="n"/>
+      <c r="Z86" s="16" t="n"/>
+      <c r="AA86" s="16" t="n"/>
       <c r="AB86" s="16" t="n"/>
-      <c r="AC86" s="16" t="n"/>
-      <c r="AD86" s="16" t="n"/>
-      <c r="AE86" s="16" t="n"/>
+      <c r="AC86" s="21" t="n"/>
+      <c r="AD86" s="21" t="n"/>
+      <c r="AE86" s="21" t="n"/>
       <c r="AF86" s="16" t="n"/>
       <c r="AG86" s="16" t="n"/>
       <c r="AH86" s="16" t="n"/>
@@ -7326,7 +7326,7 @@
       <c r="B88" s="22" t="n"/>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: [전체 일정관리] 근무 스케줄 등록</t>
+          <t>↳ 실제 진행: [전체 일정관리] 근무 스케줄 등록</t>
         </is>
       </c>
       <c r="D88" s="19" t="inlineStr">
@@ -7335,14 +7335,14 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="F88" s="20" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="G88" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 2일 단축 완료</t>
+          <t>계획 대비 1일 단축 완료</t>
         </is>
       </c>
       <c r="H88" s="16" t="n"/>
@@ -7365,12 +7365,12 @@
       <c r="Y88" s="16" t="n"/>
       <c r="Z88" s="16" t="n"/>
       <c r="AA88" s="16" t="n"/>
-      <c r="AB88" s="21" t="n"/>
+      <c r="AB88" s="16" t="n"/>
       <c r="AC88" s="16" t="n"/>
       <c r="AD88" s="16" t="n"/>
       <c r="AE88" s="16" t="n"/>
-      <c r="AF88" s="16" t="n"/>
-      <c r="AG88" s="16" t="n"/>
+      <c r="AF88" s="21" t="n"/>
+      <c r="AG88" s="21" t="n"/>
       <c r="AH88" s="16" t="n"/>
       <c r="AI88" s="16" t="n"/>
       <c r="AJ88" s="16" t="n"/>
@@ -7482,7 +7482,7 @@
       <c r="B90" s="17" t="n"/>
       <c r="C90" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: 프론트엔드 화면 통합 (SPA 라우팅, 공통 UI)</t>
+          <t>↳ 실제 진행: 프론트엔드 화면 통합 (SPA 라우팅, 공통 UI)</t>
         </is>
       </c>
       <c r="D90" s="19" t="inlineStr">
@@ -7494,11 +7494,11 @@
         <v>46281</v>
       </c>
       <c r="F90" s="20" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="G90" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 3일 단축 완료</t>
+          <t>계획 대비 2일 단축 완료</t>
         </is>
       </c>
       <c r="H90" s="16" t="n"/>
@@ -7533,7 +7533,7 @@
       <c r="AK90" s="16" t="n"/>
       <c r="AL90" s="21" t="n"/>
       <c r="AM90" s="21" t="n"/>
-      <c r="AN90" s="16" t="n"/>
+      <c r="AN90" s="21" t="n"/>
       <c r="AO90" s="16" t="n"/>
       <c r="AP90" s="16" t="n"/>
       <c r="AQ90" s="16" t="n"/>
@@ -7634,7 +7634,7 @@
       <c r="B92" s="22" t="n"/>
       <c r="C92" s="18" t="inlineStr">
         <is>
-          <t>↳ AI 활용 실제 진행: 기능 통합 및 1차 자체 QA</t>
+          <t>↳ 실제 진행: 기능 통합 및 1차 자체 QA</t>
         </is>
       </c>
       <c r="D92" s="19" t="inlineStr">
@@ -7646,11 +7646,11 @@
         <v>46281</v>
       </c>
       <c r="F92" s="20" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="G92" s="18" t="inlineStr">
         <is>
-          <t>AI 페어프로그래밍 활용, 계획 대비 3일 단축 완료</t>
+          <t>계획 대비 2일 단축 완료</t>
         </is>
       </c>
       <c r="H92" s="16" t="n"/>
@@ -7685,7 +7685,7 @@
       <c r="AK92" s="16" t="n"/>
       <c r="AL92" s="21" t="n"/>
       <c r="AM92" s="21" t="n"/>
-      <c r="AN92" s="16" t="n"/>
+      <c r="AN92" s="21" t="n"/>
       <c r="AO92" s="16" t="n"/>
       <c r="AP92" s="16" t="n"/>
       <c r="AQ92" s="16" t="n"/>
@@ -7853,25 +7853,25 @@
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="B95" s="17" t="n"/>
-      <c r="C95" s="13" t="inlineStr">
-        <is>
-          <t>기능별 테스트 및 버그 리포트</t>
-        </is>
-      </c>
-      <c r="D95" s="12" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="E95" s="14" t="n">
+      <c r="C95" s="18" t="inlineStr">
+        <is>
+          <t>↳ 실제 진행: 통합테스트 시나리오 작성</t>
+        </is>
+      </c>
+      <c r="D95" s="19" t="inlineStr">
+        <is>
+          <t>이원준</t>
+        </is>
+      </c>
+      <c r="E95" s="20" t="n">
         <v>46286</v>
       </c>
-      <c r="F95" s="14" t="n">
-        <v>46290</v>
-      </c>
-      <c r="G95" s="13" t="inlineStr">
-        <is>
-          <t>버그 리포트</t>
+      <c r="F95" s="20" t="n">
+        <v>46287</v>
+      </c>
+      <c r="G95" s="18" t="inlineStr">
+        <is>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H95" s="16" t="n"/>
@@ -7909,11 +7909,11 @@
       <c r="AN95" s="16" t="n"/>
       <c r="AO95" s="16" t="n"/>
       <c r="AP95" s="16" t="n"/>
-      <c r="AQ95" s="15" t="n"/>
-      <c r="AR95" s="15" t="n"/>
-      <c r="AS95" s="15" t="n"/>
-      <c r="AT95" s="15" t="n"/>
-      <c r="AU95" s="15" t="n"/>
+      <c r="AQ95" s="21" t="n"/>
+      <c r="AR95" s="21" t="n"/>
+      <c r="AS95" s="16" t="n"/>
+      <c r="AT95" s="16" t="n"/>
+      <c r="AU95" s="16" t="n"/>
       <c r="AV95" s="16" t="n"/>
       <c r="AW95" s="16" t="n"/>
       <c r="AX95" s="16" t="n"/>
@@ -7931,23 +7931,23 @@
       <c r="B96" s="17" t="n"/>
       <c r="C96" s="13" t="inlineStr">
         <is>
-          <t>버그 수정</t>
+          <t>기능별 테스트 및 버그 리포트</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>각 담당자</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="F96" s="14" t="n">
-        <v>46292</v>
+        <v>46290</v>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
-          <t>수정 완료 빌드</t>
+          <t>버그 리포트</t>
         </is>
       </c>
       <c r="H96" s="16" t="n"/>
@@ -7985,13 +7985,13 @@
       <c r="AN96" s="16" t="n"/>
       <c r="AO96" s="16" t="n"/>
       <c r="AP96" s="16" t="n"/>
-      <c r="AQ96" s="16" t="n"/>
-      <c r="AR96" s="16" t="n"/>
+      <c r="AQ96" s="15" t="n"/>
+      <c r="AR96" s="15" t="n"/>
       <c r="AS96" s="15" t="n"/>
       <c r="AT96" s="15" t="n"/>
       <c r="AU96" s="15" t="n"/>
-      <c r="AV96" s="15" t="n"/>
-      <c r="AW96" s="15" t="n"/>
+      <c r="AV96" s="16" t="n"/>
+      <c r="AW96" s="16" t="n"/>
       <c r="AX96" s="16" t="n"/>
       <c r="AY96" s="16" t="n"/>
       <c r="AZ96" s="16" t="n"/>
@@ -8003,27 +8003,27 @@
       <c r="BF96" s="16" t="n"/>
       <c r="BG96" s="16" t="n"/>
     </row>
-    <row r="97" ht="34" customHeight="1">
-      <c r="B97" s="22" t="n"/>
-      <c r="C97" s="13" t="inlineStr">
-        <is>
-          <t>Mock 모드 / 예외처리 점검 (Gemini API 장애 대비)</t>
-        </is>
-      </c>
-      <c r="D97" s="12" t="inlineStr">
-        <is>
-          <t>이원준</t>
-        </is>
-      </c>
-      <c r="E97" s="14" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F97" s="14" t="n">
-        <v>46291</v>
-      </c>
-      <c r="G97" s="13" t="inlineStr">
-        <is>
-          <t>예외처리 점검표</t>
+    <row r="97" ht="15" customHeight="1">
+      <c r="B97" s="17" t="n"/>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>↳ 실제 진행: 기능별 테스트 및 버그 리포트</t>
+        </is>
+      </c>
+      <c r="D97" s="19" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="E97" s="20" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F97" s="20" t="n">
+        <v>46290</v>
+      </c>
+      <c r="G97" s="18" t="inlineStr">
+        <is>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H97" s="16" t="n"/>
@@ -8061,12 +8061,12 @@
       <c r="AN97" s="16" t="n"/>
       <c r="AO97" s="16" t="n"/>
       <c r="AP97" s="16" t="n"/>
-      <c r="AQ97" s="16" t="n"/>
-      <c r="AR97" s="16" t="n"/>
-      <c r="AS97" s="16" t="n"/>
-      <c r="AT97" s="15" t="n"/>
-      <c r="AU97" s="15" t="n"/>
-      <c r="AV97" s="15" t="n"/>
+      <c r="AQ97" s="21" t="n"/>
+      <c r="AR97" s="21" t="n"/>
+      <c r="AS97" s="21" t="n"/>
+      <c r="AT97" s="21" t="n"/>
+      <c r="AU97" s="21" t="n"/>
+      <c r="AV97" s="16" t="n"/>
       <c r="AW97" s="16" t="n"/>
       <c r="AX97" s="16" t="n"/>
       <c r="AY97" s="16" t="n"/>
@@ -8080,95 +8080,102 @@
       <c r="BG97" s="16" t="n"/>
     </row>
     <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>5.0 배포/발표</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="n"/>
-      <c r="C98" s="11" t="n"/>
-      <c r="D98" s="11" t="n"/>
-      <c r="E98" s="11" t="n"/>
-      <c r="F98" s="11" t="n"/>
-      <c r="G98" s="11" t="n"/>
-      <c r="H98" s="11" t="n"/>
-      <c r="I98" s="11" t="n"/>
-      <c r="J98" s="11" t="n"/>
-      <c r="K98" s="11" t="n"/>
-      <c r="L98" s="11" t="n"/>
-      <c r="M98" s="11" t="n"/>
-      <c r="N98" s="11" t="n"/>
-      <c r="O98" s="11" t="n"/>
-      <c r="P98" s="11" t="n"/>
-      <c r="Q98" s="11" t="n"/>
-      <c r="R98" s="11" t="n"/>
-      <c r="S98" s="11" t="n"/>
-      <c r="T98" s="11" t="n"/>
-      <c r="U98" s="11" t="n"/>
-      <c r="V98" s="11" t="n"/>
-      <c r="W98" s="11" t="n"/>
-      <c r="X98" s="11" t="n"/>
-      <c r="Y98" s="11" t="n"/>
-      <c r="Z98" s="11" t="n"/>
-      <c r="AA98" s="11" t="n"/>
-      <c r="AB98" s="11" t="n"/>
-      <c r="AC98" s="11" t="n"/>
-      <c r="AD98" s="11" t="n"/>
-      <c r="AE98" s="11" t="n"/>
-      <c r="AF98" s="11" t="n"/>
-      <c r="AG98" s="11" t="n"/>
-      <c r="AH98" s="11" t="n"/>
-      <c r="AI98" s="11" t="n"/>
-      <c r="AJ98" s="11" t="n"/>
-      <c r="AK98" s="11" t="n"/>
-      <c r="AL98" s="11" t="n"/>
-      <c r="AM98" s="11" t="n"/>
-      <c r="AN98" s="11" t="n"/>
-      <c r="AO98" s="11" t="n"/>
-      <c r="AP98" s="11" t="n"/>
-      <c r="AQ98" s="11" t="n"/>
-      <c r="AR98" s="11" t="n"/>
-      <c r="AS98" s="11" t="n"/>
-      <c r="AT98" s="11" t="n"/>
-      <c r="AU98" s="11" t="n"/>
-      <c r="AV98" s="11" t="n"/>
-      <c r="AW98" s="11" t="n"/>
-      <c r="AX98" s="11" t="n"/>
-      <c r="AY98" s="11" t="n"/>
-      <c r="AZ98" s="11" t="n"/>
-      <c r="BA98" s="11" t="n"/>
-      <c r="BB98" s="11" t="n"/>
-      <c r="BC98" s="11" t="n"/>
-      <c r="BD98" s="11" t="n"/>
-      <c r="BE98" s="11" t="n"/>
-      <c r="BF98" s="11" t="n"/>
-      <c r="BG98" s="11" t="n"/>
-    </row>
-    <row r="99" ht="26" customHeight="1">
-      <c r="B99" s="12" t="inlineStr">
-        <is>
-          <t>배포 / 발표</t>
-        </is>
-      </c>
-      <c r="C99" s="13" t="inlineStr">
-        <is>
-          <t>배포 (운영환경 전환, MySQL 반영)</t>
-        </is>
-      </c>
-      <c r="D99" s="12" t="inlineStr">
-        <is>
-          <t>유충열</t>
-        </is>
-      </c>
-      <c r="E99" s="14" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F99" s="14" t="n">
-        <v>46296</v>
-      </c>
-      <c r="G99" s="13" t="inlineStr">
-        <is>
-          <t>배포 완료</t>
+      <c r="B98" s="17" t="n"/>
+      <c r="C98" s="13" t="inlineStr">
+        <is>
+          <t>버그 수정</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>각 담당자</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F98" s="14" t="n">
+        <v>46292</v>
+      </c>
+      <c r="G98" s="13" t="inlineStr">
+        <is>
+          <t>수정 완료 빌드</t>
+        </is>
+      </c>
+      <c r="H98" s="16" t="n"/>
+      <c r="I98" s="16" t="n"/>
+      <c r="J98" s="16" t="n"/>
+      <c r="K98" s="16" t="n"/>
+      <c r="L98" s="16" t="n"/>
+      <c r="M98" s="16" t="n"/>
+      <c r="N98" s="16" t="n"/>
+      <c r="O98" s="16" t="n"/>
+      <c r="P98" s="16" t="n"/>
+      <c r="Q98" s="16" t="n"/>
+      <c r="R98" s="16" t="n"/>
+      <c r="S98" s="16" t="n"/>
+      <c r="T98" s="16" t="n"/>
+      <c r="U98" s="16" t="n"/>
+      <c r="V98" s="16" t="n"/>
+      <c r="W98" s="16" t="n"/>
+      <c r="X98" s="16" t="n"/>
+      <c r="Y98" s="16" t="n"/>
+      <c r="Z98" s="16" t="n"/>
+      <c r="AA98" s="16" t="n"/>
+      <c r="AB98" s="16" t="n"/>
+      <c r="AC98" s="16" t="n"/>
+      <c r="AD98" s="16" t="n"/>
+      <c r="AE98" s="16" t="n"/>
+      <c r="AF98" s="16" t="n"/>
+      <c r="AG98" s="16" t="n"/>
+      <c r="AH98" s="16" t="n"/>
+      <c r="AI98" s="16" t="n"/>
+      <c r="AJ98" s="16" t="n"/>
+      <c r="AK98" s="16" t="n"/>
+      <c r="AL98" s="16" t="n"/>
+      <c r="AM98" s="16" t="n"/>
+      <c r="AN98" s="16" t="n"/>
+      <c r="AO98" s="16" t="n"/>
+      <c r="AP98" s="16" t="n"/>
+      <c r="AQ98" s="16" t="n"/>
+      <c r="AR98" s="16" t="n"/>
+      <c r="AS98" s="15" t="n"/>
+      <c r="AT98" s="15" t="n"/>
+      <c r="AU98" s="15" t="n"/>
+      <c r="AV98" s="15" t="n"/>
+      <c r="AW98" s="15" t="n"/>
+      <c r="AX98" s="16" t="n"/>
+      <c r="AY98" s="16" t="n"/>
+      <c r="AZ98" s="16" t="n"/>
+      <c r="BA98" s="16" t="n"/>
+      <c r="BB98" s="16" t="n"/>
+      <c r="BC98" s="16" t="n"/>
+      <c r="BD98" s="16" t="n"/>
+      <c r="BE98" s="16" t="n"/>
+      <c r="BF98" s="16" t="n"/>
+      <c r="BG98" s="16" t="n"/>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="B99" s="17" t="n"/>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>↳ 실제 진행: 버그 수정</t>
+        </is>
+      </c>
+      <c r="D99" s="19" t="inlineStr">
+        <is>
+          <t>각 담당자</t>
+        </is>
+      </c>
+      <c r="E99" s="20" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F99" s="20" t="n">
+        <v>46292</v>
+      </c>
+      <c r="G99" s="18" t="inlineStr">
+        <is>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H99" s="16" t="n"/>
@@ -8208,15 +8215,15 @@
       <c r="AP99" s="16" t="n"/>
       <c r="AQ99" s="16" t="n"/>
       <c r="AR99" s="16" t="n"/>
-      <c r="AS99" s="16" t="n"/>
-      <c r="AT99" s="16" t="n"/>
-      <c r="AU99" s="16" t="n"/>
-      <c r="AV99" s="16" t="n"/>
-      <c r="AW99" s="16" t="n"/>
+      <c r="AS99" s="21" t="n"/>
+      <c r="AT99" s="21" t="n"/>
+      <c r="AU99" s="21" t="n"/>
+      <c r="AV99" s="21" t="n"/>
+      <c r="AW99" s="21" t="n"/>
       <c r="AX99" s="16" t="n"/>
       <c r="AY99" s="16" t="n"/>
       <c r="AZ99" s="16" t="n"/>
-      <c r="BA99" s="15" t="n"/>
+      <c r="BA99" s="16" t="n"/>
       <c r="BB99" s="16" t="n"/>
       <c r="BC99" s="16" t="n"/>
       <c r="BD99" s="16" t="n"/>
@@ -8224,27 +8231,27 @@
       <c r="BF99" s="16" t="n"/>
       <c r="BG99" s="16" t="n"/>
     </row>
-    <row r="100" ht="15" customHeight="1">
+    <row r="100" ht="34" customHeight="1">
       <c r="B100" s="17" t="n"/>
       <c r="C100" s="13" t="inlineStr">
         <is>
-          <t>발표자료 (PPT) 제작</t>
+          <t>Mock 모드 / 예외처리 점검 (Gemini API 장애 대비)</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>김가현</t>
+          <t>이원준</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
-        <v>46297</v>
+        <v>46289</v>
       </c>
       <c r="F100" s="14" t="n">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
-          <t>발표 PPT</t>
+          <t>예외처리 점검표</t>
         </is>
       </c>
       <c r="H100" s="16" t="n"/>
@@ -8285,42 +8292,42 @@
       <c r="AQ100" s="16" t="n"/>
       <c r="AR100" s="16" t="n"/>
       <c r="AS100" s="16" t="n"/>
-      <c r="AT100" s="16" t="n"/>
-      <c r="AU100" s="16" t="n"/>
-      <c r="AV100" s="16" t="n"/>
+      <c r="AT100" s="15" t="n"/>
+      <c r="AU100" s="15" t="n"/>
+      <c r="AV100" s="15" t="n"/>
       <c r="AW100" s="16" t="n"/>
       <c r="AX100" s="16" t="n"/>
       <c r="AY100" s="16" t="n"/>
       <c r="AZ100" s="16" t="n"/>
       <c r="BA100" s="16" t="n"/>
-      <c r="BB100" s="15" t="n"/>
-      <c r="BC100" s="15" t="n"/>
+      <c r="BB100" s="16" t="n"/>
+      <c r="BC100" s="16" t="n"/>
       <c r="BD100" s="16" t="n"/>
       <c r="BE100" s="16" t="n"/>
       <c r="BF100" s="16" t="n"/>
       <c r="BG100" s="16" t="n"/>
     </row>
-    <row r="101" ht="15" customHeight="1">
-      <c r="B101" s="17" t="n"/>
-      <c r="C101" s="13" t="inlineStr">
-        <is>
-          <t>최종 리허설</t>
-        </is>
-      </c>
-      <c r="D101" s="12" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="E101" s="14" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F101" s="14" t="n">
-        <v>46301</v>
-      </c>
-      <c r="G101" s="13" t="inlineStr">
-        <is>
-          <t>리허설 완료</t>
+    <row r="101" ht="34" customHeight="1">
+      <c r="B101" s="22" t="n"/>
+      <c r="C101" s="18" t="inlineStr">
+        <is>
+          <t>↳ 실제 진행: Mock 모드 / 예외처리 점검 (Gemini API 장애 대비)</t>
+        </is>
+      </c>
+      <c r="D101" s="19" t="inlineStr">
+        <is>
+          <t>이원준</t>
+        </is>
+      </c>
+      <c r="E101" s="20" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F101" s="20" t="n">
+        <v>46291</v>
+      </c>
+      <c r="G101" s="18" t="inlineStr">
+        <is>
+          <t>계획대로 완료</t>
         </is>
       </c>
       <c r="H101" s="16" t="n"/>
@@ -8361,9 +8368,9 @@
       <c r="AQ101" s="16" t="n"/>
       <c r="AR101" s="16" t="n"/>
       <c r="AS101" s="16" t="n"/>
-      <c r="AT101" s="16" t="n"/>
-      <c r="AU101" s="16" t="n"/>
-      <c r="AV101" s="16" t="n"/>
+      <c r="AT101" s="21" t="n"/>
+      <c r="AU101" s="21" t="n"/>
+      <c r="AV101" s="21" t="n"/>
       <c r="AW101" s="16" t="n"/>
       <c r="AX101" s="16" t="n"/>
       <c r="AY101" s="16" t="n"/>
@@ -8373,339 +8380,804 @@
       <c r="BC101" s="16" t="n"/>
       <c r="BD101" s="16" t="n"/>
       <c r="BE101" s="16" t="n"/>
-      <c r="BF101" s="15" t="n"/>
+      <c r="BF101" s="16" t="n"/>
       <c r="BG101" s="16" t="n"/>
     </row>
     <row r="102" ht="15" customHeight="1">
-      <c r="B102" s="22" t="n"/>
-      <c r="C102" s="13" t="inlineStr">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>5.0 배포/발표</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="n"/>
+      <c r="C102" s="11" t="n"/>
+      <c r="D102" s="11" t="n"/>
+      <c r="E102" s="11" t="n"/>
+      <c r="F102" s="11" t="n"/>
+      <c r="G102" s="11" t="n"/>
+      <c r="H102" s="11" t="n"/>
+      <c r="I102" s="11" t="n"/>
+      <c r="J102" s="11" t="n"/>
+      <c r="K102" s="11" t="n"/>
+      <c r="L102" s="11" t="n"/>
+      <c r="M102" s="11" t="n"/>
+      <c r="N102" s="11" t="n"/>
+      <c r="O102" s="11" t="n"/>
+      <c r="P102" s="11" t="n"/>
+      <c r="Q102" s="11" t="n"/>
+      <c r="R102" s="11" t="n"/>
+      <c r="S102" s="11" t="n"/>
+      <c r="T102" s="11" t="n"/>
+      <c r="U102" s="11" t="n"/>
+      <c r="V102" s="11" t="n"/>
+      <c r="W102" s="11" t="n"/>
+      <c r="X102" s="11" t="n"/>
+      <c r="Y102" s="11" t="n"/>
+      <c r="Z102" s="11" t="n"/>
+      <c r="AA102" s="11" t="n"/>
+      <c r="AB102" s="11" t="n"/>
+      <c r="AC102" s="11" t="n"/>
+      <c r="AD102" s="11" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="11" t="n"/>
+      <c r="AG102" s="11" t="n"/>
+      <c r="AH102" s="11" t="n"/>
+      <c r="AI102" s="11" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="11" t="n"/>
+      <c r="AL102" s="11" t="n"/>
+      <c r="AM102" s="11" t="n"/>
+      <c r="AN102" s="11" t="n"/>
+      <c r="AO102" s="11" t="n"/>
+      <c r="AP102" s="11" t="n"/>
+      <c r="AQ102" s="11" t="n"/>
+      <c r="AR102" s="11" t="n"/>
+      <c r="AS102" s="11" t="n"/>
+      <c r="AT102" s="11" t="n"/>
+      <c r="AU102" s="11" t="n"/>
+      <c r="AV102" s="11" t="n"/>
+      <c r="AW102" s="11" t="n"/>
+      <c r="AX102" s="11" t="n"/>
+      <c r="AY102" s="11" t="n"/>
+      <c r="AZ102" s="11" t="n"/>
+      <c r="BA102" s="11" t="n"/>
+      <c r="BB102" s="11" t="n"/>
+      <c r="BC102" s="11" t="n"/>
+      <c r="BD102" s="11" t="n"/>
+      <c r="BE102" s="11" t="n"/>
+      <c r="BF102" s="11" t="n"/>
+      <c r="BG102" s="11" t="n"/>
+    </row>
+    <row r="103" ht="26" customHeight="1">
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>배포 / 발표</t>
+        </is>
+      </c>
+      <c r="C103" s="13" t="inlineStr">
+        <is>
+          <t>배포 (운영환경 전환, MySQL 반영)</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>유충열</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F103" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="G103" s="13" t="inlineStr">
+        <is>
+          <t>배포 완료</t>
+        </is>
+      </c>
+      <c r="H103" s="16" t="n"/>
+      <c r="I103" s="16" t="n"/>
+      <c r="J103" s="16" t="n"/>
+      <c r="K103" s="16" t="n"/>
+      <c r="L103" s="16" t="n"/>
+      <c r="M103" s="16" t="n"/>
+      <c r="N103" s="16" t="n"/>
+      <c r="O103" s="16" t="n"/>
+      <c r="P103" s="16" t="n"/>
+      <c r="Q103" s="16" t="n"/>
+      <c r="R103" s="16" t="n"/>
+      <c r="S103" s="16" t="n"/>
+      <c r="T103" s="16" t="n"/>
+      <c r="U103" s="16" t="n"/>
+      <c r="V103" s="16" t="n"/>
+      <c r="W103" s="16" t="n"/>
+      <c r="X103" s="16" t="n"/>
+      <c r="Y103" s="16" t="n"/>
+      <c r="Z103" s="16" t="n"/>
+      <c r="AA103" s="16" t="n"/>
+      <c r="AB103" s="16" t="n"/>
+      <c r="AC103" s="16" t="n"/>
+      <c r="AD103" s="16" t="n"/>
+      <c r="AE103" s="16" t="n"/>
+      <c r="AF103" s="16" t="n"/>
+      <c r="AG103" s="16" t="n"/>
+      <c r="AH103" s="16" t="n"/>
+      <c r="AI103" s="16" t="n"/>
+      <c r="AJ103" s="16" t="n"/>
+      <c r="AK103" s="16" t="n"/>
+      <c r="AL103" s="16" t="n"/>
+      <c r="AM103" s="16" t="n"/>
+      <c r="AN103" s="16" t="n"/>
+      <c r="AO103" s="16" t="n"/>
+      <c r="AP103" s="16" t="n"/>
+      <c r="AQ103" s="16" t="n"/>
+      <c r="AR103" s="16" t="n"/>
+      <c r="AS103" s="16" t="n"/>
+      <c r="AT103" s="16" t="n"/>
+      <c r="AU103" s="16" t="n"/>
+      <c r="AV103" s="16" t="n"/>
+      <c r="AW103" s="16" t="n"/>
+      <c r="AX103" s="16" t="n"/>
+      <c r="AY103" s="16" t="n"/>
+      <c r="AZ103" s="15" t="n"/>
+      <c r="BA103" s="16" t="n"/>
+      <c r="BB103" s="16" t="n"/>
+      <c r="BC103" s="16" t="n"/>
+      <c r="BD103" s="16" t="n"/>
+      <c r="BE103" s="16" t="n"/>
+      <c r="BF103" s="16" t="n"/>
+      <c r="BG103" s="16" t="n"/>
+    </row>
+    <row r="104" ht="26" customHeight="1">
+      <c r="B104" s="17" t="n"/>
+      <c r="C104" s="18" t="inlineStr">
+        <is>
+          <t>↳ 실제 진행: 배포 (운영환경 전환, MySQL 반영)</t>
+        </is>
+      </c>
+      <c r="D104" s="19" t="inlineStr">
+        <is>
+          <t>유충열</t>
+        </is>
+      </c>
+      <c r="E104" s="20" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F104" s="20" t="n">
+        <v>46295</v>
+      </c>
+      <c r="G104" s="18" t="inlineStr">
+        <is>
+          <t>일부 미완 — H2 파일 DB 유지(MySQL 미전환), 로컬 실행까지 진행</t>
+        </is>
+      </c>
+      <c r="H104" s="16" t="n"/>
+      <c r="I104" s="16" t="n"/>
+      <c r="J104" s="16" t="n"/>
+      <c r="K104" s="16" t="n"/>
+      <c r="L104" s="16" t="n"/>
+      <c r="M104" s="16" t="n"/>
+      <c r="N104" s="16" t="n"/>
+      <c r="O104" s="16" t="n"/>
+      <c r="P104" s="16" t="n"/>
+      <c r="Q104" s="16" t="n"/>
+      <c r="R104" s="16" t="n"/>
+      <c r="S104" s="16" t="n"/>
+      <c r="T104" s="16" t="n"/>
+      <c r="U104" s="16" t="n"/>
+      <c r="V104" s="16" t="n"/>
+      <c r="W104" s="16" t="n"/>
+      <c r="X104" s="16" t="n"/>
+      <c r="Y104" s="16" t="n"/>
+      <c r="Z104" s="16" t="n"/>
+      <c r="AA104" s="16" t="n"/>
+      <c r="AB104" s="16" t="n"/>
+      <c r="AC104" s="16" t="n"/>
+      <c r="AD104" s="16" t="n"/>
+      <c r="AE104" s="16" t="n"/>
+      <c r="AF104" s="16" t="n"/>
+      <c r="AG104" s="16" t="n"/>
+      <c r="AH104" s="16" t="n"/>
+      <c r="AI104" s="16" t="n"/>
+      <c r="AJ104" s="16" t="n"/>
+      <c r="AK104" s="16" t="n"/>
+      <c r="AL104" s="16" t="n"/>
+      <c r="AM104" s="16" t="n"/>
+      <c r="AN104" s="16" t="n"/>
+      <c r="AO104" s="16" t="n"/>
+      <c r="AP104" s="16" t="n"/>
+      <c r="AQ104" s="16" t="n"/>
+      <c r="AR104" s="16" t="n"/>
+      <c r="AS104" s="16" t="n"/>
+      <c r="AT104" s="16" t="n"/>
+      <c r="AU104" s="16" t="n"/>
+      <c r="AV104" s="16" t="n"/>
+      <c r="AW104" s="16" t="n"/>
+      <c r="AX104" s="16" t="n"/>
+      <c r="AY104" s="16" t="n"/>
+      <c r="AZ104" s="21" t="n"/>
+      <c r="BA104" s="16" t="n"/>
+      <c r="BB104" s="16" t="n"/>
+      <c r="BC104" s="16" t="n"/>
+      <c r="BD104" s="16" t="n"/>
+      <c r="BE104" s="16" t="n"/>
+      <c r="BF104" s="16" t="n"/>
+      <c r="BG104" s="16" t="n"/>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="B105" s="17" t="n"/>
+      <c r="C105" s="13" t="inlineStr">
+        <is>
+          <t>발표자료 (PPT) 제작</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>김가현</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F105" s="14" t="n">
+        <v>46298</v>
+      </c>
+      <c r="G105" s="13" t="inlineStr">
+        <is>
+          <t>발표 PPT</t>
+        </is>
+      </c>
+      <c r="H105" s="16" t="n"/>
+      <c r="I105" s="16" t="n"/>
+      <c r="J105" s="16" t="n"/>
+      <c r="K105" s="16" t="n"/>
+      <c r="L105" s="16" t="n"/>
+      <c r="M105" s="16" t="n"/>
+      <c r="N105" s="16" t="n"/>
+      <c r="O105" s="16" t="n"/>
+      <c r="P105" s="16" t="n"/>
+      <c r="Q105" s="16" t="n"/>
+      <c r="R105" s="16" t="n"/>
+      <c r="S105" s="16" t="n"/>
+      <c r="T105" s="16" t="n"/>
+      <c r="U105" s="16" t="n"/>
+      <c r="V105" s="16" t="n"/>
+      <c r="W105" s="16" t="n"/>
+      <c r="X105" s="16" t="n"/>
+      <c r="Y105" s="16" t="n"/>
+      <c r="Z105" s="16" t="n"/>
+      <c r="AA105" s="16" t="n"/>
+      <c r="AB105" s="16" t="n"/>
+      <c r="AC105" s="16" t="n"/>
+      <c r="AD105" s="16" t="n"/>
+      <c r="AE105" s="16" t="n"/>
+      <c r="AF105" s="16" t="n"/>
+      <c r="AG105" s="16" t="n"/>
+      <c r="AH105" s="16" t="n"/>
+      <c r="AI105" s="16" t="n"/>
+      <c r="AJ105" s="16" t="n"/>
+      <c r="AK105" s="16" t="n"/>
+      <c r="AL105" s="16" t="n"/>
+      <c r="AM105" s="16" t="n"/>
+      <c r="AN105" s="16" t="n"/>
+      <c r="AO105" s="16" t="n"/>
+      <c r="AP105" s="16" t="n"/>
+      <c r="AQ105" s="16" t="n"/>
+      <c r="AR105" s="16" t="n"/>
+      <c r="AS105" s="16" t="n"/>
+      <c r="AT105" s="16" t="n"/>
+      <c r="AU105" s="16" t="n"/>
+      <c r="AV105" s="16" t="n"/>
+      <c r="AW105" s="16" t="n"/>
+      <c r="AX105" s="16" t="n"/>
+      <c r="AY105" s="16" t="n"/>
+      <c r="AZ105" s="16" t="n"/>
+      <c r="BA105" s="16" t="n"/>
+      <c r="BB105" s="15" t="n"/>
+      <c r="BC105" s="15" t="n"/>
+      <c r="BD105" s="16" t="n"/>
+      <c r="BE105" s="16" t="n"/>
+      <c r="BF105" s="16" t="n"/>
+      <c r="BG105" s="16" t="n"/>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="B106" s="17" t="n"/>
+      <c r="C106" s="18" t="inlineStr">
+        <is>
+          <t>↳ 실제 진행: 발표자료 (PPT) 제작</t>
+        </is>
+      </c>
+      <c r="D106" s="19" t="inlineStr">
+        <is>
+          <t>김가현</t>
+        </is>
+      </c>
+      <c r="E106" s="20" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F106" s="20" t="n">
+        <v>46298</v>
+      </c>
+      <c r="G106" s="18" t="inlineStr">
+        <is>
+          <t>계획대로 완료</t>
+        </is>
+      </c>
+      <c r="H106" s="16" t="n"/>
+      <c r="I106" s="16" t="n"/>
+      <c r="J106" s="16" t="n"/>
+      <c r="K106" s="16" t="n"/>
+      <c r="L106" s="16" t="n"/>
+      <c r="M106" s="16" t="n"/>
+      <c r="N106" s="16" t="n"/>
+      <c r="O106" s="16" t="n"/>
+      <c r="P106" s="16" t="n"/>
+      <c r="Q106" s="16" t="n"/>
+      <c r="R106" s="16" t="n"/>
+      <c r="S106" s="16" t="n"/>
+      <c r="T106" s="16" t="n"/>
+      <c r="U106" s="16" t="n"/>
+      <c r="V106" s="16" t="n"/>
+      <c r="W106" s="16" t="n"/>
+      <c r="X106" s="16" t="n"/>
+      <c r="Y106" s="16" t="n"/>
+      <c r="Z106" s="16" t="n"/>
+      <c r="AA106" s="16" t="n"/>
+      <c r="AB106" s="16" t="n"/>
+      <c r="AC106" s="16" t="n"/>
+      <c r="AD106" s="16" t="n"/>
+      <c r="AE106" s="16" t="n"/>
+      <c r="AF106" s="16" t="n"/>
+      <c r="AG106" s="16" t="n"/>
+      <c r="AH106" s="16" t="n"/>
+      <c r="AI106" s="16" t="n"/>
+      <c r="AJ106" s="16" t="n"/>
+      <c r="AK106" s="16" t="n"/>
+      <c r="AL106" s="16" t="n"/>
+      <c r="AM106" s="16" t="n"/>
+      <c r="AN106" s="16" t="n"/>
+      <c r="AO106" s="16" t="n"/>
+      <c r="AP106" s="16" t="n"/>
+      <c r="AQ106" s="16" t="n"/>
+      <c r="AR106" s="16" t="n"/>
+      <c r="AS106" s="16" t="n"/>
+      <c r="AT106" s="16" t="n"/>
+      <c r="AU106" s="16" t="n"/>
+      <c r="AV106" s="16" t="n"/>
+      <c r="AW106" s="16" t="n"/>
+      <c r="AX106" s="16" t="n"/>
+      <c r="AY106" s="16" t="n"/>
+      <c r="AZ106" s="16" t="n"/>
+      <c r="BA106" s="16" t="n"/>
+      <c r="BB106" s="21" t="n"/>
+      <c r="BC106" s="21" t="n"/>
+      <c r="BD106" s="16" t="n"/>
+      <c r="BE106" s="16" t="n"/>
+      <c r="BF106" s="16" t="n"/>
+      <c r="BG106" s="16" t="n"/>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="B107" s="17" t="n"/>
+      <c r="C107" s="13" t="inlineStr">
+        <is>
+          <t>최종 리허설</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="E107" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F107" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="G107" s="13" t="inlineStr">
+        <is>
+          <t>리허설 완료</t>
+        </is>
+      </c>
+      <c r="H107" s="16" t="n"/>
+      <c r="I107" s="16" t="n"/>
+      <c r="J107" s="16" t="n"/>
+      <c r="K107" s="16" t="n"/>
+      <c r="L107" s="16" t="n"/>
+      <c r="M107" s="16" t="n"/>
+      <c r="N107" s="16" t="n"/>
+      <c r="O107" s="16" t="n"/>
+      <c r="P107" s="16" t="n"/>
+      <c r="Q107" s="16" t="n"/>
+      <c r="R107" s="16" t="n"/>
+      <c r="S107" s="16" t="n"/>
+      <c r="T107" s="16" t="n"/>
+      <c r="U107" s="16" t="n"/>
+      <c r="V107" s="16" t="n"/>
+      <c r="W107" s="16" t="n"/>
+      <c r="X107" s="16" t="n"/>
+      <c r="Y107" s="16" t="n"/>
+      <c r="Z107" s="16" t="n"/>
+      <c r="AA107" s="16" t="n"/>
+      <c r="AB107" s="16" t="n"/>
+      <c r="AC107" s="16" t="n"/>
+      <c r="AD107" s="16" t="n"/>
+      <c r="AE107" s="16" t="n"/>
+      <c r="AF107" s="16" t="n"/>
+      <c r="AG107" s="16" t="n"/>
+      <c r="AH107" s="16" t="n"/>
+      <c r="AI107" s="16" t="n"/>
+      <c r="AJ107" s="16" t="n"/>
+      <c r="AK107" s="16" t="n"/>
+      <c r="AL107" s="16" t="n"/>
+      <c r="AM107" s="16" t="n"/>
+      <c r="AN107" s="16" t="n"/>
+      <c r="AO107" s="16" t="n"/>
+      <c r="AP107" s="16" t="n"/>
+      <c r="AQ107" s="16" t="n"/>
+      <c r="AR107" s="16" t="n"/>
+      <c r="AS107" s="16" t="n"/>
+      <c r="AT107" s="16" t="n"/>
+      <c r="AU107" s="16" t="n"/>
+      <c r="AV107" s="16" t="n"/>
+      <c r="AW107" s="16" t="n"/>
+      <c r="AX107" s="16" t="n"/>
+      <c r="AY107" s="16" t="n"/>
+      <c r="AZ107" s="16" t="n"/>
+      <c r="BA107" s="16" t="n"/>
+      <c r="BB107" s="16" t="n"/>
+      <c r="BC107" s="16" t="n"/>
+      <c r="BD107" s="16" t="n"/>
+      <c r="BE107" s="16" t="n"/>
+      <c r="BF107" s="15" t="n"/>
+      <c r="BG107" s="16" t="n"/>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="B108" s="17" t="n"/>
+      <c r="C108" s="18" t="inlineStr">
+        <is>
+          <t>↳ 실제 진행: 최종 리허설</t>
+        </is>
+      </c>
+      <c r="D108" s="19" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="E108" s="20" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F108" s="20" t="n">
+        <v>46301</v>
+      </c>
+      <c r="G108" s="18" t="inlineStr">
+        <is>
+          <t>계획대로 완료</t>
+        </is>
+      </c>
+      <c r="H108" s="16" t="n"/>
+      <c r="I108" s="16" t="n"/>
+      <c r="J108" s="16" t="n"/>
+      <c r="K108" s="16" t="n"/>
+      <c r="L108" s="16" t="n"/>
+      <c r="M108" s="16" t="n"/>
+      <c r="N108" s="16" t="n"/>
+      <c r="O108" s="16" t="n"/>
+      <c r="P108" s="16" t="n"/>
+      <c r="Q108" s="16" t="n"/>
+      <c r="R108" s="16" t="n"/>
+      <c r="S108" s="16" t="n"/>
+      <c r="T108" s="16" t="n"/>
+      <c r="U108" s="16" t="n"/>
+      <c r="V108" s="16" t="n"/>
+      <c r="W108" s="16" t="n"/>
+      <c r="X108" s="16" t="n"/>
+      <c r="Y108" s="16" t="n"/>
+      <c r="Z108" s="16" t="n"/>
+      <c r="AA108" s="16" t="n"/>
+      <c r="AB108" s="16" t="n"/>
+      <c r="AC108" s="16" t="n"/>
+      <c r="AD108" s="16" t="n"/>
+      <c r="AE108" s="16" t="n"/>
+      <c r="AF108" s="16" t="n"/>
+      <c r="AG108" s="16" t="n"/>
+      <c r="AH108" s="16" t="n"/>
+      <c r="AI108" s="16" t="n"/>
+      <c r="AJ108" s="16" t="n"/>
+      <c r="AK108" s="16" t="n"/>
+      <c r="AL108" s="16" t="n"/>
+      <c r="AM108" s="16" t="n"/>
+      <c r="AN108" s="16" t="n"/>
+      <c r="AO108" s="16" t="n"/>
+      <c r="AP108" s="16" t="n"/>
+      <c r="AQ108" s="16" t="n"/>
+      <c r="AR108" s="16" t="n"/>
+      <c r="AS108" s="16" t="n"/>
+      <c r="AT108" s="16" t="n"/>
+      <c r="AU108" s="16" t="n"/>
+      <c r="AV108" s="16" t="n"/>
+      <c r="AW108" s="16" t="n"/>
+      <c r="AX108" s="16" t="n"/>
+      <c r="AY108" s="16" t="n"/>
+      <c r="AZ108" s="16" t="n"/>
+      <c r="BA108" s="16" t="n"/>
+      <c r="BB108" s="16" t="n"/>
+      <c r="BC108" s="16" t="n"/>
+      <c r="BD108" s="16" t="n"/>
+      <c r="BE108" s="16" t="n"/>
+      <c r="BF108" s="21" t="n"/>
+      <c r="BG108" s="16" t="n"/>
+    </row>
+    <row r="109" ht="15" customHeight="1">
+      <c r="B109" s="17" t="n"/>
+      <c r="C109" s="13" t="inlineStr">
         <is>
           <t>최종 발표</t>
         </is>
       </c>
-      <c r="D102" s="12" t="inlineStr">
+      <c r="D109" s="12" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="E102" s="14" t="n">
+      <c r="E109" s="14" t="n">
         <v>46302</v>
       </c>
-      <c r="F102" s="14" t="n">
+      <c r="F109" s="14" t="n">
         <v>46302</v>
       </c>
-      <c r="G102" s="13" t="inlineStr">
+      <c r="G109" s="13" t="inlineStr">
         <is>
           <t>발표 완료</t>
         </is>
       </c>
-      <c r="H102" s="16" t="n"/>
-      <c r="I102" s="16" t="n"/>
-      <c r="J102" s="16" t="n"/>
-      <c r="K102" s="16" t="n"/>
-      <c r="L102" s="16" t="n"/>
-      <c r="M102" s="16" t="n"/>
-      <c r="N102" s="16" t="n"/>
-      <c r="O102" s="16" t="n"/>
-      <c r="P102" s="16" t="n"/>
-      <c r="Q102" s="16" t="n"/>
-      <c r="R102" s="16" t="n"/>
-      <c r="S102" s="16" t="n"/>
-      <c r="T102" s="16" t="n"/>
-      <c r="U102" s="16" t="n"/>
-      <c r="V102" s="16" t="n"/>
-      <c r="W102" s="16" t="n"/>
-      <c r="X102" s="16" t="n"/>
-      <c r="Y102" s="16" t="n"/>
-      <c r="Z102" s="16" t="n"/>
-      <c r="AA102" s="16" t="n"/>
-      <c r="AB102" s="16" t="n"/>
-      <c r="AC102" s="16" t="n"/>
-      <c r="AD102" s="16" t="n"/>
-      <c r="AE102" s="16" t="n"/>
-      <c r="AF102" s="16" t="n"/>
-      <c r="AG102" s="16" t="n"/>
-      <c r="AH102" s="16" t="n"/>
-      <c r="AI102" s="16" t="n"/>
-      <c r="AJ102" s="16" t="n"/>
-      <c r="AK102" s="16" t="n"/>
-      <c r="AL102" s="16" t="n"/>
-      <c r="AM102" s="16" t="n"/>
-      <c r="AN102" s="16" t="n"/>
-      <c r="AO102" s="16" t="n"/>
-      <c r="AP102" s="16" t="n"/>
-      <c r="AQ102" s="16" t="n"/>
-      <c r="AR102" s="16" t="n"/>
-      <c r="AS102" s="16" t="n"/>
-      <c r="AT102" s="16" t="n"/>
-      <c r="AU102" s="16" t="n"/>
-      <c r="AV102" s="16" t="n"/>
-      <c r="AW102" s="16" t="n"/>
-      <c r="AX102" s="16" t="n"/>
-      <c r="AY102" s="16" t="n"/>
-      <c r="AZ102" s="16" t="n"/>
-      <c r="BA102" s="16" t="n"/>
-      <c r="BB102" s="16" t="n"/>
-      <c r="BC102" s="16" t="n"/>
-      <c r="BD102" s="16" t="n"/>
-      <c r="BE102" s="16" t="n"/>
-      <c r="BF102" s="16" t="n"/>
-      <c r="BG102" s="15" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="10" t="inlineStr">
+      <c r="H109" s="16" t="n"/>
+      <c r="I109" s="16" t="n"/>
+      <c r="J109" s="16" t="n"/>
+      <c r="K109" s="16" t="n"/>
+      <c r="L109" s="16" t="n"/>
+      <c r="M109" s="16" t="n"/>
+      <c r="N109" s="16" t="n"/>
+      <c r="O109" s="16" t="n"/>
+      <c r="P109" s="16" t="n"/>
+      <c r="Q109" s="16" t="n"/>
+      <c r="R109" s="16" t="n"/>
+      <c r="S109" s="16" t="n"/>
+      <c r="T109" s="16" t="n"/>
+      <c r="U109" s="16" t="n"/>
+      <c r="V109" s="16" t="n"/>
+      <c r="W109" s="16" t="n"/>
+      <c r="X109" s="16" t="n"/>
+      <c r="Y109" s="16" t="n"/>
+      <c r="Z109" s="16" t="n"/>
+      <c r="AA109" s="16" t="n"/>
+      <c r="AB109" s="16" t="n"/>
+      <c r="AC109" s="16" t="n"/>
+      <c r="AD109" s="16" t="n"/>
+      <c r="AE109" s="16" t="n"/>
+      <c r="AF109" s="16" t="n"/>
+      <c r="AG109" s="16" t="n"/>
+      <c r="AH109" s="16" t="n"/>
+      <c r="AI109" s="16" t="n"/>
+      <c r="AJ109" s="16" t="n"/>
+      <c r="AK109" s="16" t="n"/>
+      <c r="AL109" s="16" t="n"/>
+      <c r="AM109" s="16" t="n"/>
+      <c r="AN109" s="16" t="n"/>
+      <c r="AO109" s="16" t="n"/>
+      <c r="AP109" s="16" t="n"/>
+      <c r="AQ109" s="16" t="n"/>
+      <c r="AR109" s="16" t="n"/>
+      <c r="AS109" s="16" t="n"/>
+      <c r="AT109" s="16" t="n"/>
+      <c r="AU109" s="16" t="n"/>
+      <c r="AV109" s="16" t="n"/>
+      <c r="AW109" s="16" t="n"/>
+      <c r="AX109" s="16" t="n"/>
+      <c r="AY109" s="16" t="n"/>
+      <c r="AZ109" s="16" t="n"/>
+      <c r="BA109" s="16" t="n"/>
+      <c r="BB109" s="16" t="n"/>
+      <c r="BC109" s="16" t="n"/>
+      <c r="BD109" s="16" t="n"/>
+      <c r="BE109" s="16" t="n"/>
+      <c r="BF109" s="16" t="n"/>
+      <c r="BG109" s="15" t="n"/>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="B110" s="22" t="n"/>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>↳ 실제 진행: 최종 발표</t>
+        </is>
+      </c>
+      <c r="D110" s="19" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="E110" s="20" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F110" s="20" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G110" s="18" t="inlineStr">
+        <is>
+          <t>계획대로 완료</t>
+        </is>
+      </c>
+      <c r="H110" s="16" t="n"/>
+      <c r="I110" s="16" t="n"/>
+      <c r="J110" s="16" t="n"/>
+      <c r="K110" s="16" t="n"/>
+      <c r="L110" s="16" t="n"/>
+      <c r="M110" s="16" t="n"/>
+      <c r="N110" s="16" t="n"/>
+      <c r="O110" s="16" t="n"/>
+      <c r="P110" s="16" t="n"/>
+      <c r="Q110" s="16" t="n"/>
+      <c r="R110" s="16" t="n"/>
+      <c r="S110" s="16" t="n"/>
+      <c r="T110" s="16" t="n"/>
+      <c r="U110" s="16" t="n"/>
+      <c r="V110" s="16" t="n"/>
+      <c r="W110" s="16" t="n"/>
+      <c r="X110" s="16" t="n"/>
+      <c r="Y110" s="16" t="n"/>
+      <c r="Z110" s="16" t="n"/>
+      <c r="AA110" s="16" t="n"/>
+      <c r="AB110" s="16" t="n"/>
+      <c r="AC110" s="16" t="n"/>
+      <c r="AD110" s="16" t="n"/>
+      <c r="AE110" s="16" t="n"/>
+      <c r="AF110" s="16" t="n"/>
+      <c r="AG110" s="16" t="n"/>
+      <c r="AH110" s="16" t="n"/>
+      <c r="AI110" s="16" t="n"/>
+      <c r="AJ110" s="16" t="n"/>
+      <c r="AK110" s="16" t="n"/>
+      <c r="AL110" s="16" t="n"/>
+      <c r="AM110" s="16" t="n"/>
+      <c r="AN110" s="16" t="n"/>
+      <c r="AO110" s="16" t="n"/>
+      <c r="AP110" s="16" t="n"/>
+      <c r="AQ110" s="16" t="n"/>
+      <c r="AR110" s="16" t="n"/>
+      <c r="AS110" s="16" t="n"/>
+      <c r="AT110" s="16" t="n"/>
+      <c r="AU110" s="16" t="n"/>
+      <c r="AV110" s="16" t="n"/>
+      <c r="AW110" s="16" t="n"/>
+      <c r="AX110" s="16" t="n"/>
+      <c r="AY110" s="16" t="n"/>
+      <c r="AZ110" s="16" t="n"/>
+      <c r="BA110" s="16" t="n"/>
+      <c r="BB110" s="16" t="n"/>
+      <c r="BC110" s="16" t="n"/>
+      <c r="BD110" s="16" t="n"/>
+      <c r="BE110" s="16" t="n"/>
+      <c r="BF110" s="16" t="n"/>
+      <c r="BG110" s="21" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
         <is>
           <t>6.0 기능 / 화면 상세 분해</t>
         </is>
       </c>
-      <c r="B104" s="11" t="n"/>
-      <c r="C104" s="11" t="n"/>
-      <c r="D104" s="11" t="n"/>
-      <c r="E104" s="11" t="n"/>
-      <c r="F104" s="11" t="n"/>
-      <c r="G104" s="11" t="n"/>
-      <c r="H104" s="11" t="n"/>
-      <c r="I104" s="11" t="n"/>
-      <c r="J104" s="11" t="n"/>
-      <c r="K104" s="11" t="n"/>
-      <c r="L104" s="11" t="n"/>
-      <c r="M104" s="11" t="n"/>
-      <c r="N104" s="11" t="n"/>
-      <c r="O104" s="11" t="n"/>
-      <c r="P104" s="11" t="n"/>
-      <c r="Q104" s="11" t="n"/>
-      <c r="R104" s="11" t="n"/>
-      <c r="S104" s="11" t="n"/>
-      <c r="T104" s="11" t="n"/>
-      <c r="U104" s="11" t="n"/>
-      <c r="V104" s="11" t="n"/>
-      <c r="W104" s="11" t="n"/>
-      <c r="X104" s="11" t="n"/>
-      <c r="Y104" s="11" t="n"/>
-      <c r="Z104" s="11" t="n"/>
-      <c r="AA104" s="11" t="n"/>
-      <c r="AB104" s="11" t="n"/>
-      <c r="AC104" s="11" t="n"/>
-      <c r="AD104" s="11" t="n"/>
-      <c r="AE104" s="11" t="n"/>
-      <c r="AF104" s="11" t="n"/>
-      <c r="AG104" s="11" t="n"/>
-      <c r="AH104" s="11" t="n"/>
-      <c r="AI104" s="11" t="n"/>
-      <c r="AJ104" s="11" t="n"/>
-      <c r="AK104" s="11" t="n"/>
-      <c r="AL104" s="11" t="n"/>
-      <c r="AM104" s="11" t="n"/>
-      <c r="AN104" s="11" t="n"/>
-      <c r="AO104" s="11" t="n"/>
-      <c r="AP104" s="11" t="n"/>
-      <c r="AQ104" s="11" t="n"/>
-      <c r="AR104" s="11" t="n"/>
-      <c r="AS104" s="11" t="n"/>
-      <c r="AT104" s="11" t="n"/>
-      <c r="AU104" s="11" t="n"/>
-      <c r="AV104" s="11" t="n"/>
-      <c r="AW104" s="11" t="n"/>
-      <c r="AX104" s="11" t="n"/>
-      <c r="AY104" s="11" t="n"/>
-      <c r="AZ104" s="11" t="n"/>
-      <c r="BA104" s="11" t="n"/>
-      <c r="BB104" s="11" t="n"/>
-      <c r="BC104" s="11" t="n"/>
-      <c r="BD104" s="11" t="n"/>
-      <c r="BE104" s="11" t="n"/>
-      <c r="BF104" s="11" t="n"/>
-      <c r="BG104" s="11" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="23" t="inlineStr">
+      <c r="B112" s="11" t="n"/>
+      <c r="C112" s="11" t="n"/>
+      <c r="D112" s="11" t="n"/>
+      <c r="E112" s="11" t="n"/>
+      <c r="F112" s="11" t="n"/>
+      <c r="G112" s="11" t="n"/>
+      <c r="H112" s="11" t="n"/>
+      <c r="I112" s="11" t="n"/>
+      <c r="J112" s="11" t="n"/>
+      <c r="K112" s="11" t="n"/>
+      <c r="L112" s="11" t="n"/>
+      <c r="M112" s="11" t="n"/>
+      <c r="N112" s="11" t="n"/>
+      <c r="O112" s="11" t="n"/>
+      <c r="P112" s="11" t="n"/>
+      <c r="Q112" s="11" t="n"/>
+      <c r="R112" s="11" t="n"/>
+      <c r="S112" s="11" t="n"/>
+      <c r="T112" s="11" t="n"/>
+      <c r="U112" s="11" t="n"/>
+      <c r="V112" s="11" t="n"/>
+      <c r="W112" s="11" t="n"/>
+      <c r="X112" s="11" t="n"/>
+      <c r="Y112" s="11" t="n"/>
+      <c r="Z112" s="11" t="n"/>
+      <c r="AA112" s="11" t="n"/>
+      <c r="AB112" s="11" t="n"/>
+      <c r="AC112" s="11" t="n"/>
+      <c r="AD112" s="11" t="n"/>
+      <c r="AE112" s="11" t="n"/>
+      <c r="AF112" s="11" t="n"/>
+      <c r="AG112" s="11" t="n"/>
+      <c r="AH112" s="11" t="n"/>
+      <c r="AI112" s="11" t="n"/>
+      <c r="AJ112" s="11" t="n"/>
+      <c r="AK112" s="11" t="n"/>
+      <c r="AL112" s="11" t="n"/>
+      <c r="AM112" s="11" t="n"/>
+      <c r="AN112" s="11" t="n"/>
+      <c r="AO112" s="11" t="n"/>
+      <c r="AP112" s="11" t="n"/>
+      <c r="AQ112" s="11" t="n"/>
+      <c r="AR112" s="11" t="n"/>
+      <c r="AS112" s="11" t="n"/>
+      <c r="AT112" s="11" t="n"/>
+      <c r="AU112" s="11" t="n"/>
+      <c r="AV112" s="11" t="n"/>
+      <c r="AW112" s="11" t="n"/>
+      <c r="AX112" s="11" t="n"/>
+      <c r="AY112" s="11" t="n"/>
+      <c r="AZ112" s="11" t="n"/>
+      <c r="BA112" s="11" t="n"/>
+      <c r="BB112" s="11" t="n"/>
+      <c r="BC112" s="11" t="n"/>
+      <c r="BD112" s="11" t="n"/>
+      <c r="BE112" s="11" t="n"/>
+      <c r="BF112" s="11" t="n"/>
+      <c r="BG112" s="11" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="23" t="inlineStr">
         <is>
           <t>대분류</t>
         </is>
       </c>
-      <c r="B105" s="23" t="inlineStr">
+      <c r="B113" s="23" t="inlineStr">
         <is>
           <t>중분류</t>
         </is>
       </c>
-      <c r="C105" s="23" t="inlineStr">
+      <c r="C113" s="23" t="inlineStr">
         <is>
           <t>소분류</t>
         </is>
       </c>
-      <c r="D105" s="23" t="inlineStr">
+      <c r="D113" s="23" t="inlineStr">
         <is>
           <t>세분류</t>
         </is>
       </c>
-      <c r="E105" s="23" t="inlineStr">
+      <c r="E113" s="23" t="inlineStr">
         <is>
           <t>세분류 체크항목</t>
         </is>
       </c>
-      <c r="F105" s="24" t="n"/>
-      <c r="G105" s="24" t="n"/>
-    </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="23" t="inlineStr">
+      <c r="F113" s="24" t="n"/>
+      <c r="G113" s="24" t="n"/>
+    </row>
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="23" t="inlineStr">
         <is>
           <t>공통 (인증)</t>
         </is>
       </c>
-      <c r="B106" s="12" t="inlineStr">
+      <c r="B114" s="12" t="inlineStr">
         <is>
           <t>회원가입 · 로그인</t>
         </is>
       </c>
-      <c r="C106" s="12" t="inlineStr">
+      <c r="C114" s="12" t="inlineStr">
         <is>
           <t>매장 등록 및 회원가입</t>
         </is>
       </c>
-      <c r="D106" s="12" t="inlineStr">
+      <c r="D114" s="12" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="E106" s="13" t="inlineStr">
+      <c r="E114" s="13" t="inlineStr">
         <is>
           <t>매장정보 입력</t>
-        </is>
-      </c>
-      <c r="F106" s="12" t="n"/>
-      <c r="G106" s="12" t="n"/>
-    </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="17" t="n"/>
-      <c r="B107" s="17" t="n"/>
-      <c r="C107" s="17" t="n"/>
-      <c r="D107" s="17" t="n"/>
-      <c r="E107" s="13" t="inlineStr">
-        <is>
-          <t>이메일/비밀번호 입력</t>
-        </is>
-      </c>
-      <c r="F107" s="12" t="n"/>
-      <c r="G107" s="12" t="n"/>
-    </row>
-    <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="17" t="n"/>
-      <c r="B108" s="17" t="n"/>
-      <c r="C108" s="17" t="n"/>
-      <c r="D108" s="22" t="n"/>
-      <c r="E108" s="13" t="inlineStr">
-        <is>
-          <t>유효성 검사</t>
-        </is>
-      </c>
-      <c r="F108" s="12" t="n"/>
-      <c r="G108" s="12" t="n"/>
-    </row>
-    <row r="109" ht="24" customHeight="1">
-      <c r="A109" s="17" t="n"/>
-      <c r="B109" s="17" t="n"/>
-      <c r="C109" s="22" t="n"/>
-      <c r="D109" s="12" t="inlineStr">
-        <is>
-          <t>가입승인 대기</t>
-        </is>
-      </c>
-      <c r="E109" s="13" t="inlineStr">
-        <is>
-          <t>승인 전 접근 제한 안내</t>
-        </is>
-      </c>
-      <c r="F109" s="12" t="n"/>
-      <c r="G109" s="12" t="n"/>
-    </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="17" t="n"/>
-      <c r="B110" s="17" t="n"/>
-      <c r="C110" s="12" t="inlineStr">
-        <is>
-          <t>로그인</t>
-        </is>
-      </c>
-      <c r="D110" s="12" t="inlineStr">
-        <is>
-          <t>로그인</t>
-        </is>
-      </c>
-      <c r="E110" s="13" t="inlineStr">
-        <is>
-          <t>세션 생성</t>
-        </is>
-      </c>
-      <c r="F110" s="12" t="n"/>
-      <c r="G110" s="12" t="n"/>
-    </row>
-    <row r="111" ht="24" customHeight="1">
-      <c r="A111" s="17" t="n"/>
-      <c r="B111" s="17" t="n"/>
-      <c r="C111" s="17" t="n"/>
-      <c r="D111" s="22" t="n"/>
-      <c r="E111" s="13" t="inlineStr">
-        <is>
-          <t>권한별(직원/사장) 리다이렉트</t>
-        </is>
-      </c>
-      <c r="F111" s="12" t="n"/>
-      <c r="G111" s="12" t="n"/>
-    </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="22" t="n"/>
-      <c r="B112" s="22" t="n"/>
-      <c r="C112" s="22" t="n"/>
-      <c r="D112" s="12" t="inlineStr">
-        <is>
-          <t>로그아웃</t>
-        </is>
-      </c>
-      <c r="E112" s="13" t="inlineStr">
-        <is>
-          <t>세션 종료</t>
-        </is>
-      </c>
-      <c r="F112" s="12" t="n"/>
-      <c r="G112" s="12" t="n"/>
-    </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="23" t="inlineStr">
-        <is>
-          <t>사장 (관리자)</t>
-        </is>
-      </c>
-      <c r="B113" s="12" t="inlineStr">
-        <is>
-          <t>관리자 대시보드</t>
-        </is>
-      </c>
-      <c r="C113" s="12" t="inlineStr">
-        <is>
-          <t>대시보드</t>
-        </is>
-      </c>
-      <c r="D113" s="12" t="inlineStr">
-        <is>
-          <t>조회</t>
-        </is>
-      </c>
-      <c r="E113" s="13" t="inlineStr">
-        <is>
-          <t>예약 현황 요약</t>
-        </is>
-      </c>
-      <c r="F113" s="12" t="n"/>
-      <c r="G113" s="12" t="n"/>
-    </row>
-    <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="17" t="n"/>
-      <c r="B114" s="17" t="n"/>
-      <c r="C114" s="17" t="n"/>
-      <c r="D114" s="17" t="n"/>
-      <c r="E114" s="13" t="inlineStr">
-        <is>
-          <t>재고 현황 요약</t>
         </is>
       </c>
       <c r="F114" s="12" t="n"/>
@@ -8713,12 +9185,12 @@
     </row>
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="17" t="n"/>
-      <c r="B115" s="22" t="n"/>
-      <c r="C115" s="22" t="n"/>
-      <c r="D115" s="22" t="n"/>
+      <c r="B115" s="17" t="n"/>
+      <c r="C115" s="17" t="n"/>
+      <c r="D115" s="17" t="n"/>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>실시간 갱신</t>
+          <t>이메일/비밀번호 입력</t>
         </is>
       </c>
       <c r="F115" s="12" t="n"/>
@@ -8726,37 +9198,29 @@
     </row>
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="17" t="n"/>
-      <c r="B116" s="12" t="inlineStr">
-        <is>
-          <t>직원관리</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="inlineStr">
-        <is>
-          <t>가입승인</t>
-        </is>
-      </c>
-      <c r="D116" s="12" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
+      <c r="B116" s="17" t="n"/>
+      <c r="C116" s="17" t="n"/>
+      <c r="D116" s="22" t="n"/>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>승인대기 목록</t>
+          <t>유효성 검사</t>
         </is>
       </c>
       <c r="F116" s="12" t="n"/>
       <c r="G116" s="12" t="n"/>
     </row>
-    <row r="117" ht="16" customHeight="1">
+    <row r="117" ht="24" customHeight="1">
       <c r="A117" s="17" t="n"/>
       <c r="B117" s="17" t="n"/>
-      <c r="C117" s="17" t="n"/>
-      <c r="D117" s="22" t="n"/>
+      <c r="C117" s="22" t="n"/>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>가입승인 대기</t>
+        </is>
+      </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>페이징</t>
+          <t>승인 전 접근 제한 안내</t>
         </is>
       </c>
       <c r="F117" s="12" t="n"/>
@@ -8765,133 +9229,129 @@
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="17" t="n"/>
       <c r="B118" s="17" t="n"/>
-      <c r="C118" s="17" t="n"/>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>승인 / 거절</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>승인 처리</t>
+          <t>세션 생성</t>
         </is>
       </c>
       <c r="F118" s="12" t="n"/>
       <c r="G118" s="12" t="n"/>
     </row>
-    <row r="119" ht="16" customHeight="1">
+    <row r="119" ht="24" customHeight="1">
       <c r="A119" s="17" t="n"/>
       <c r="B119" s="17" t="n"/>
-      <c r="C119" s="22" t="n"/>
+      <c r="C119" s="17" t="n"/>
       <c r="D119" s="22" t="n"/>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>거절 사유 입력</t>
+          <t>권한별(직원/사장) 리다이렉트</t>
         </is>
       </c>
       <c r="F119" s="12" t="n"/>
       <c r="G119" s="12" t="n"/>
     </row>
-    <row r="120" ht="24" customHeight="1">
-      <c r="A120" s="17" t="n"/>
-      <c r="B120" s="17" t="n"/>
-      <c r="C120" s="12" t="inlineStr">
-        <is>
-          <t>근태관리</t>
-        </is>
-      </c>
+    <row r="120" ht="16" customHeight="1">
+      <c r="A120" s="22" t="n"/>
+      <c r="B120" s="22" t="n"/>
+      <c r="C120" s="22" t="n"/>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>퇴직 / 복직 처리</t>
+          <t>로그아웃</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>상태 변경</t>
+          <t>세션 종료</t>
         </is>
       </c>
       <c r="F120" s="12" t="n"/>
       <c r="G120" s="12" t="n"/>
     </row>
-    <row r="121" ht="24" customHeight="1">
-      <c r="A121" s="17" t="n"/>
-      <c r="B121" s="22" t="n"/>
-      <c r="C121" s="22" t="n"/>
-      <c r="D121" s="22" t="n"/>
+    <row r="121" ht="16" customHeight="1">
+      <c r="A121" s="23" t="inlineStr">
+        <is>
+          <t>사장 (관리자)</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>관리자 대시보드</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>대시보드</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>조회</t>
+        </is>
+      </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>이력 기록</t>
+          <t>예약 현황 요약</t>
         </is>
       </c>
       <c r="F121" s="12" t="n"/>
       <c r="G121" s="12" t="n"/>
     </row>
-    <row r="122" ht="24" customHeight="1">
+    <row r="122" ht="16" customHeight="1">
       <c r="A122" s="17" t="n"/>
-      <c r="B122" s="12" t="inlineStr">
-        <is>
-          <t>전체 일정관리</t>
-        </is>
-      </c>
-      <c r="C122" s="12" t="inlineStr">
-        <is>
-          <t>통합 캘린더</t>
-        </is>
-      </c>
-      <c r="D122" s="12" t="inlineStr">
-        <is>
-          <t>조회</t>
-        </is>
-      </c>
+      <c r="B122" s="17" t="n"/>
+      <c r="C122" s="17" t="n"/>
+      <c r="D122" s="17" t="n"/>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>공지 · 예약 · 근무스케줄 통합 표시</t>
+          <t>재고 현황 요약</t>
         </is>
       </c>
       <c r="F122" s="12" t="n"/>
       <c r="G122" s="12" t="n"/>
     </row>
     <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="22" t="n"/>
+      <c r="A123" s="17" t="n"/>
       <c r="B123" s="22" t="n"/>
       <c r="C123" s="22" t="n"/>
-      <c r="D123" s="12" t="inlineStr">
-        <is>
-          <t>등록</t>
-        </is>
-      </c>
+      <c r="D123" s="22" t="n"/>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>근무 스케줄 등록</t>
+          <t>실시간 갱신</t>
         </is>
       </c>
       <c r="F123" s="12" t="n"/>
       <c r="G123" s="12" t="n"/>
     </row>
     <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="23" t="inlineStr">
-        <is>
-          <t>직원 (User)</t>
-        </is>
-      </c>
+      <c r="A124" s="17" t="n"/>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>재고관리</t>
+          <t>직원관리</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
+          <t>가입승인</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
           <t>목록</t>
         </is>
       </c>
-      <c r="D124" s="12" t="inlineStr">
-        <is>
-          <t>조회</t>
-        </is>
-      </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>재고 목록</t>
+          <t>승인대기 목록</t>
         </is>
       </c>
       <c r="F124" s="12" t="n"/>
@@ -8900,11 +9360,11 @@
     <row r="125" ht="16" customHeight="1">
       <c r="A125" s="17" t="n"/>
       <c r="B125" s="17" t="n"/>
-      <c r="C125" s="22" t="n"/>
+      <c r="C125" s="17" t="n"/>
       <c r="D125" s="22" t="n"/>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>재고 부족 하이라이트</t>
+          <t>페이징</t>
         </is>
       </c>
       <c r="F125" s="12" t="n"/>
@@ -8913,19 +9373,15 @@
     <row r="126" ht="16" customHeight="1">
       <c r="A126" s="17" t="n"/>
       <c r="B126" s="17" t="n"/>
-      <c r="C126" s="12" t="inlineStr">
-        <is>
-          <t>입고</t>
-        </is>
-      </c>
+      <c r="C126" s="17" t="n"/>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>승인 / 거절</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>품목 · 수량 입력</t>
+          <t>승인 처리</t>
         </is>
       </c>
       <c r="F126" s="12" t="n"/>
@@ -8938,41 +9394,41 @@
       <c r="D127" s="22" t="n"/>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>변동 이력 기록</t>
+          <t>거절 사유 입력</t>
         </is>
       </c>
       <c r="F127" s="12" t="n"/>
       <c r="G127" s="12" t="n"/>
     </row>
-    <row r="128" ht="16" customHeight="1">
+    <row r="128" ht="24" customHeight="1">
       <c r="A128" s="17" t="n"/>
       <c r="B128" s="17" t="n"/>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>폐기</t>
+          <t>근태관리</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>퇴직 / 복직 처리</t>
         </is>
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>폐기 사유 입력</t>
+          <t>상태 변경</t>
         </is>
       </c>
       <c r="F128" s="12" t="n"/>
       <c r="G128" s="12" t="n"/>
     </row>
-    <row r="129" ht="16" customHeight="1">
+    <row r="129" ht="24" customHeight="1">
       <c r="A129" s="17" t="n"/>
-      <c r="B129" s="17" t="n"/>
+      <c r="B129" s="22" t="n"/>
       <c r="C129" s="22" t="n"/>
       <c r="D129" s="22" t="n"/>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>변동 이력 기록</t>
+          <t>이력 기록</t>
         </is>
       </c>
       <c r="F129" s="12" t="n"/>
@@ -8980,54 +9436,70 @@
     </row>
     <row r="130" ht="24" customHeight="1">
       <c r="A130" s="17" t="n"/>
-      <c r="B130" s="17" t="n"/>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>전체 일정관리</t>
+        </is>
+      </c>
       <c r="C130" s="12" t="inlineStr">
         <is>
-          <t>AI 재고실사</t>
+          <t>통합 캘린더</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>사진 촬영 / 업로드</t>
+          <t>조회</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>이미지 첨부</t>
+          <t>공지 · 예약 · 근무스케줄 통합 표시</t>
         </is>
       </c>
       <c r="F130" s="12" t="n"/>
       <c r="G130" s="12" t="n"/>
     </row>
-    <row r="131" ht="24" customHeight="1">
-      <c r="A131" s="17" t="n"/>
-      <c r="B131" s="17" t="n"/>
-      <c r="C131" s="17" t="n"/>
+    <row r="131" ht="16" customHeight="1">
+      <c r="A131" s="22" t="n"/>
+      <c r="B131" s="22" t="n"/>
+      <c r="C131" s="22" t="n"/>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>AI 인식결과 검토</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>인식 수량 표시</t>
+          <t>근무 스케줄 등록</t>
         </is>
       </c>
       <c r="F131" s="12" t="n"/>
       <c r="G131" s="12" t="n"/>
     </row>
     <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="17" t="n"/>
-      <c r="B132" s="17" t="n"/>
-      <c r="C132" s="17" t="n"/>
+      <c r="A132" s="23" t="inlineStr">
+        <is>
+          <t>직원 (User)</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t>재고관리</t>
+        </is>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>보정</t>
+          <t>조회</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>수동 수정</t>
+          <t>재고 목록</t>
         </is>
       </c>
       <c r="F132" s="12" t="n"/>
@@ -9035,31 +9507,23 @@
     </row>
     <row r="133" ht="16" customHeight="1">
       <c r="A133" s="17" t="n"/>
-      <c r="B133" s="22" t="n"/>
+      <c r="B133" s="17" t="n"/>
       <c r="C133" s="22" t="n"/>
-      <c r="D133" s="12" t="inlineStr">
-        <is>
-          <t>확정 반영</t>
-        </is>
-      </c>
+      <c r="D133" s="22" t="n"/>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>재고 데이터 갱신</t>
+          <t>재고 부족 하이라이트</t>
         </is>
       </c>
       <c r="F133" s="12" t="n"/>
       <c r="G133" s="12" t="n"/>
     </row>
-    <row r="134" ht="24" customHeight="1">
+    <row r="134" ht="16" customHeight="1">
       <c r="A134" s="17" t="n"/>
-      <c r="B134" s="12" t="inlineStr">
-        <is>
-          <t>예약관리</t>
-        </is>
-      </c>
+      <c r="B134" s="17" t="n"/>
       <c r="C134" s="12" t="inlineStr">
         <is>
-          <t>예약접수</t>
+          <t>입고</t>
         </is>
       </c>
       <c r="D134" s="12" t="inlineStr">
@@ -9069,24 +9533,20 @@
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>날짜 · 시간 · 인원 · 테이블 선택</t>
+          <t>품목 · 수량 입력</t>
         </is>
       </c>
       <c r="F134" s="12" t="n"/>
       <c r="G134" s="12" t="n"/>
     </row>
-    <row r="135" ht="24" customHeight="1">
+    <row r="135" ht="16" customHeight="1">
       <c r="A135" s="17" t="n"/>
       <c r="B135" s="17" t="n"/>
       <c r="C135" s="22" t="n"/>
-      <c r="D135" s="12" t="inlineStr">
-        <is>
-          <t>중복확인</t>
-        </is>
-      </c>
+      <c r="D135" s="22" t="n"/>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>동일 시간대 중복예약 경고</t>
+          <t>변동 이력 기록</t>
         </is>
       </c>
       <c r="F135" s="12" t="n"/>
@@ -9097,17 +9557,17 @@
       <c r="B136" s="17" t="n"/>
       <c r="C136" s="12" t="inlineStr">
         <is>
-          <t>예약조회</t>
+          <t>폐기</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>날짜별 조회</t>
+          <t>폐기 사유 입력</t>
         </is>
       </c>
       <c r="F136" s="12" t="n"/>
@@ -9116,53 +9576,49 @@
     <row r="137" ht="16" customHeight="1">
       <c r="A137" s="17" t="n"/>
       <c r="B137" s="17" t="n"/>
-      <c r="C137" s="17" t="n"/>
+      <c r="C137" s="22" t="n"/>
       <c r="D137" s="22" t="n"/>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>변동 이력 기록</t>
         </is>
       </c>
       <c r="F137" s="12" t="n"/>
       <c r="G137" s="12" t="n"/>
     </row>
-    <row r="138" ht="16" customHeight="1">
+    <row r="138" ht="24" customHeight="1">
       <c r="A138" s="17" t="n"/>
-      <c r="B138" s="22" t="n"/>
-      <c r="C138" s="22" t="n"/>
+      <c r="B138" s="17" t="n"/>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>AI 재고실사</t>
+        </is>
+      </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>수정 · 취소</t>
+          <t>사진 촬영 / 업로드</t>
         </is>
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>상태 변경</t>
+          <t>이미지 첨부</t>
         </is>
       </c>
       <c r="F138" s="12" t="n"/>
       <c r="G138" s="12" t="n"/>
     </row>
-    <row r="139" ht="16" customHeight="1">
+    <row r="139" ht="24" customHeight="1">
       <c r="A139" s="17" t="n"/>
-      <c r="B139" s="12" t="inlineStr">
-        <is>
-          <t>일보 (업무일지)</t>
-        </is>
-      </c>
-      <c r="C139" s="12" t="inlineStr">
-        <is>
-          <t>작성</t>
-        </is>
-      </c>
+      <c r="B139" s="17" t="n"/>
+      <c r="C139" s="17" t="n"/>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>AI 인식결과 검토</t>
         </is>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>근무 내용 입력</t>
+          <t>인식 수량 표시</t>
         </is>
       </c>
       <c r="F139" s="12" t="n"/>
@@ -9171,19 +9627,15 @@
     <row r="140" ht="16" customHeight="1">
       <c r="A140" s="17" t="n"/>
       <c r="B140" s="17" t="n"/>
-      <c r="C140" s="12" t="inlineStr">
-        <is>
-          <t>조회</t>
-        </is>
-      </c>
+      <c r="C140" s="17" t="n"/>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>보정</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>날짜별 조회</t>
+          <t>수동 수정</t>
         </is>
       </c>
       <c r="F140" s="12" t="n"/>
@@ -9191,50 +9643,58 @@
     </row>
     <row r="141" ht="16" customHeight="1">
       <c r="A141" s="17" t="n"/>
-      <c r="B141" s="17" t="n"/>
-      <c r="C141" s="17" t="n"/>
-      <c r="D141" s="22" t="n"/>
+      <c r="B141" s="22" t="n"/>
+      <c r="C141" s="22" t="n"/>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>확정 반영</t>
+        </is>
+      </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>페이징</t>
+          <t>재고 데이터 갱신</t>
         </is>
       </c>
       <c r="F141" s="12" t="n"/>
       <c r="G141" s="12" t="n"/>
     </row>
-    <row r="142" ht="16" customHeight="1">
+    <row r="142" ht="24" customHeight="1">
       <c r="A142" s="17" t="n"/>
-      <c r="B142" s="17" t="n"/>
-      <c r="C142" s="22" t="n"/>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t>예약관리</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>예약접수</t>
+        </is>
+      </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>상세보기</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>댓글 목록</t>
+          <t>날짜 · 시간 · 인원 · 테이블 선택</t>
         </is>
       </c>
       <c r="F142" s="12" t="n"/>
       <c r="G142" s="12" t="n"/>
     </row>
-    <row r="143" ht="16" customHeight="1">
+    <row r="143" ht="24" customHeight="1">
       <c r="A143" s="17" t="n"/>
       <c r="B143" s="17" t="n"/>
-      <c r="C143" s="12" t="inlineStr">
-        <is>
-          <t>수정 · 삭제</t>
-        </is>
-      </c>
+      <c r="C143" s="22" t="n"/>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>중복확인</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>동일 시간대 중복예약 경고</t>
         </is>
       </c>
       <c r="F143" s="12" t="n"/>
@@ -9243,15 +9703,19 @@
     <row r="144" ht="16" customHeight="1">
       <c r="A144" s="17" t="n"/>
       <c r="B144" s="17" t="n"/>
-      <c r="C144" s="22" t="n"/>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>예약조회</t>
+        </is>
+      </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>삭제</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>삭제</t>
+          <t>날짜별 조회</t>
         </is>
       </c>
       <c r="F144" s="12" t="n"/>
@@ -9259,20 +9723,12 @@
     </row>
     <row r="145" ht="16" customHeight="1">
       <c r="A145" s="17" t="n"/>
-      <c r="B145" s="22" t="n"/>
-      <c r="C145" s="12" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="D145" s="12" t="inlineStr">
-        <is>
-          <t>등록 / 삭제</t>
-        </is>
-      </c>
+      <c r="B145" s="17" t="n"/>
+      <c r="C145" s="17" t="n"/>
+      <c r="D145" s="22" t="n"/>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>댓글 CRUD</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="F145" s="12" t="n"/>
@@ -9280,24 +9736,16 @@
     </row>
     <row r="146" ht="16" customHeight="1">
       <c r="A146" s="17" t="n"/>
-      <c r="B146" s="12" t="inlineStr">
-        <is>
-          <t>공지사항</t>
-        </is>
-      </c>
-      <c r="C146" s="12" t="inlineStr">
-        <is>
-          <t>등록 (사장 전용)</t>
-        </is>
-      </c>
+      <c r="B146" s="22" t="n"/>
+      <c r="C146" s="22" t="n"/>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정 · 취소</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>제목 · 내용 입력</t>
+          <t>상태 변경</t>
         </is>
       </c>
       <c r="F146" s="12" t="n"/>
@@ -9305,37 +9753,45 @@
     </row>
     <row r="147" ht="16" customHeight="1">
       <c r="A147" s="17" t="n"/>
-      <c r="B147" s="17" t="n"/>
+      <c r="B147" s="12" t="inlineStr">
+        <is>
+          <t>일보 (업무일지)</t>
+        </is>
+      </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>작성</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>페이징</t>
+          <t>근무 내용 입력</t>
         </is>
       </c>
       <c r="F147" s="12" t="n"/>
       <c r="G147" s="12" t="n"/>
     </row>
-    <row r="148" ht="24" customHeight="1">
+    <row r="148" ht="16" customHeight="1">
       <c r="A148" s="17" t="n"/>
       <c r="B148" s="17" t="n"/>
-      <c r="C148" s="22" t="n"/>
+      <c r="C148" s="12" t="inlineStr">
+        <is>
+          <t>조회</t>
+        </is>
+      </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>상세보기</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
-          <t>확인 체크 (읽음 처리)</t>
+          <t>날짜별 조회</t>
         </is>
       </c>
       <c r="F148" s="12" t="n"/>
@@ -9343,20 +9799,12 @@
     </row>
     <row r="149" ht="16" customHeight="1">
       <c r="A149" s="17" t="n"/>
-      <c r="B149" s="22" t="n"/>
-      <c r="C149" s="12" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="D149" s="12" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
+      <c r="B149" s="17" t="n"/>
+      <c r="C149" s="17" t="n"/>
+      <c r="D149" s="22" t="n"/>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>페이징</t>
         </is>
       </c>
       <c r="F149" s="12" t="n"/>
@@ -9364,24 +9812,16 @@
     </row>
     <row r="150" ht="16" customHeight="1">
       <c r="A150" s="17" t="n"/>
-      <c r="B150" s="12" t="inlineStr">
-        <is>
-          <t>출퇴근관리</t>
-        </is>
-      </c>
-      <c r="C150" s="12" t="inlineStr">
-        <is>
-          <t>출근 / 퇴근</t>
-        </is>
-      </c>
+      <c r="B150" s="17" t="n"/>
+      <c r="C150" s="22" t="n"/>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>출근 등록</t>
+          <t>상세보기</t>
         </is>
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>출근 시간 기록</t>
+          <t>댓글 목록</t>
         </is>
       </c>
       <c r="F150" s="12" t="n"/>
@@ -9390,162 +9830,330 @@
     <row r="151" ht="16" customHeight="1">
       <c r="A151" s="17" t="n"/>
       <c r="B151" s="17" t="n"/>
-      <c r="C151" s="22" t="n"/>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>수정 · 삭제</t>
+        </is>
+      </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>퇴근 등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="E151" s="13" t="inlineStr">
         <is>
-          <t>퇴근 시간 기록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="F151" s="12" t="n"/>
       <c r="G151" s="12" t="n"/>
     </row>
-    <row r="152" ht="24" customHeight="1">
+    <row r="152" ht="16" customHeight="1">
       <c r="A152" s="17" t="n"/>
-      <c r="B152" s="22" t="n"/>
-      <c r="C152" s="12" t="inlineStr">
-        <is>
-          <t>휴게관리</t>
-        </is>
-      </c>
+      <c r="B152" s="17" t="n"/>
+      <c r="C152" s="22" t="n"/>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>휴게 시작 · 종료</t>
+          <t>삭제</t>
         </is>
       </c>
       <c r="E152" s="13" t="inlineStr">
         <is>
-          <t>휴게 시간 기록</t>
+          <t>삭제</t>
         </is>
       </c>
       <c r="F152" s="12" t="n"/>
       <c r="G152" s="12" t="n"/>
     </row>
-    <row r="153" ht="24" customHeight="1">
+    <row r="153" ht="16" customHeight="1">
       <c r="A153" s="17" t="n"/>
-      <c r="B153" s="12" t="inlineStr">
-        <is>
-          <t>알림</t>
-        </is>
-      </c>
+      <c r="B153" s="22" t="n"/>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>통합 알림</t>
+          <t>댓글</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>등록 / 삭제</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>재고부족 · 예약 · 공지 · 일보 알림 목록</t>
+          <t>댓글 CRUD</t>
         </is>
       </c>
       <c r="F153" s="12" t="n"/>
       <c r="G153" s="12" t="n"/>
     </row>
     <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="22" t="n"/>
-      <c r="B154" s="22" t="n"/>
-      <c r="C154" s="22" t="n"/>
+      <c r="A154" s="17" t="n"/>
+      <c r="B154" s="12" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="C154" s="12" t="inlineStr">
+        <is>
+          <t>등록 (사장 전용)</t>
+        </is>
+      </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>읽음 처리</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>읽음 상태 갱신</t>
+          <t>제목 · 내용 입력</t>
         </is>
       </c>
       <c r="F154" s="12" t="n"/>
       <c r="G154" s="12" t="n"/>
+    </row>
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="17" t="n"/>
+      <c r="B155" s="17" t="n"/>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>조회</t>
+        </is>
+      </c>
+      <c r="D155" s="12" t="inlineStr">
+        <is>
+          <t>목록</t>
+        </is>
+      </c>
+      <c r="E155" s="13" t="inlineStr">
+        <is>
+          <t>페이징</t>
+        </is>
+      </c>
+      <c r="F155" s="12" t="n"/>
+      <c r="G155" s="12" t="n"/>
+    </row>
+    <row r="156" ht="24" customHeight="1">
+      <c r="A156" s="17" t="n"/>
+      <c r="B156" s="17" t="n"/>
+      <c r="C156" s="22" t="n"/>
+      <c r="D156" s="12" t="inlineStr">
+        <is>
+          <t>상세보기</t>
+        </is>
+      </c>
+      <c r="E156" s="13" t="inlineStr">
+        <is>
+          <t>확인 체크 (읽음 처리)</t>
+        </is>
+      </c>
+      <c r="F156" s="12" t="n"/>
+      <c r="G156" s="12" t="n"/>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="17" t="n"/>
+      <c r="B157" s="22" t="n"/>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="D157" s="12" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="E157" s="13" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="F157" s="12" t="n"/>
+      <c r="G157" s="12" t="n"/>
+    </row>
+    <row r="158" ht="16" customHeight="1">
+      <c r="A158" s="17" t="n"/>
+      <c r="B158" s="12" t="inlineStr">
+        <is>
+          <t>출퇴근관리</t>
+        </is>
+      </c>
+      <c r="C158" s="12" t="inlineStr">
+        <is>
+          <t>출근 / 퇴근</t>
+        </is>
+      </c>
+      <c r="D158" s="12" t="inlineStr">
+        <is>
+          <t>출근 등록</t>
+        </is>
+      </c>
+      <c r="E158" s="13" t="inlineStr">
+        <is>
+          <t>출근 시간 기록</t>
+        </is>
+      </c>
+      <c r="F158" s="12" t="n"/>
+      <c r="G158" s="12" t="n"/>
+    </row>
+    <row r="159" ht="16" customHeight="1">
+      <c r="A159" s="17" t="n"/>
+      <c r="B159" s="17" t="n"/>
+      <c r="C159" s="22" t="n"/>
+      <c r="D159" s="12" t="inlineStr">
+        <is>
+          <t>퇴근 등록</t>
+        </is>
+      </c>
+      <c r="E159" s="13" t="inlineStr">
+        <is>
+          <t>퇴근 시간 기록</t>
+        </is>
+      </c>
+      <c r="F159" s="12" t="n"/>
+      <c r="G159" s="12" t="n"/>
+    </row>
+    <row r="160" ht="24" customHeight="1">
+      <c r="A160" s="17" t="n"/>
+      <c r="B160" s="22" t="n"/>
+      <c r="C160" s="12" t="inlineStr">
+        <is>
+          <t>휴게관리</t>
+        </is>
+      </c>
+      <c r="D160" s="12" t="inlineStr">
+        <is>
+          <t>휴게 시작 · 종료</t>
+        </is>
+      </c>
+      <c r="E160" s="13" t="inlineStr">
+        <is>
+          <t>휴게 시간 기록</t>
+        </is>
+      </c>
+      <c r="F160" s="12" t="n"/>
+      <c r="G160" s="12" t="n"/>
+    </row>
+    <row r="161" ht="24" customHeight="1">
+      <c r="A161" s="17" t="n"/>
+      <c r="B161" s="12" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="C161" s="12" t="inlineStr">
+        <is>
+          <t>통합 알림</t>
+        </is>
+      </c>
+      <c r="D161" s="12" t="inlineStr">
+        <is>
+          <t>조회</t>
+        </is>
+      </c>
+      <c r="E161" s="13" t="inlineStr">
+        <is>
+          <t>재고부족 · 예약 · 공지 · 일보 알림 목록</t>
+        </is>
+      </c>
+      <c r="F161" s="12" t="n"/>
+      <c r="G161" s="12" t="n"/>
+    </row>
+    <row r="162" ht="16" customHeight="1">
+      <c r="A162" s="22" t="n"/>
+      <c r="B162" s="22" t="n"/>
+      <c r="C162" s="22" t="n"/>
+      <c r="D162" s="12" t="inlineStr">
+        <is>
+          <t>읽음 처리</t>
+        </is>
+      </c>
+      <c r="E162" s="13" t="inlineStr">
+        <is>
+          <t>읽음 상태 갱신</t>
+        </is>
+      </c>
+      <c r="F162" s="12" t="n"/>
+      <c r="G162" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="78">
     <mergeCell ref="C128:C129"/>
+    <mergeCell ref="C144:C146"/>
     <mergeCell ref="C134:C135"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="D134:D135"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A106:A112"/>
-    <mergeCell ref="B139:B145"/>
-    <mergeCell ref="B150:B152"/>
-    <mergeCell ref="B116:B121"/>
-    <mergeCell ref="C113:C115"/>
+    <mergeCell ref="A114:A120"/>
     <mergeCell ref="A4:G5"/>
+    <mergeCell ref="C118:C120"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B26:B29"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="H4:V4"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="D140:D141"/>
+    <mergeCell ref="C151:C152"/>
+    <mergeCell ref="D121:D123"/>
     <mergeCell ref="AJ5:AP5"/>
+    <mergeCell ref="B130:B131"/>
     <mergeCell ref="AX5:BD5"/>
     <mergeCell ref="H5:N5"/>
     <mergeCell ref="D126:D127"/>
-    <mergeCell ref="A113:A123"/>
-    <mergeCell ref="D116:D117"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B59:B72"/>
-    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="C114:C117"/>
     <mergeCell ref="D118:D119"/>
-    <mergeCell ref="C153:C154"/>
-    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="C138:C141"/>
     <mergeCell ref="O5:U5"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="AC5:AI5"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="B124:B133"/>
-    <mergeCell ref="D106:D108"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="C110:C112"/>
-    <mergeCell ref="A124:A154"/>
-    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="A132:A162"/>
+    <mergeCell ref="D144:D145"/>
+    <mergeCell ref="B124:B129"/>
     <mergeCell ref="D136:D137"/>
+    <mergeCell ref="B158:B160"/>
     <mergeCell ref="BA4:BG4"/>
-    <mergeCell ref="C116:C119"/>
+    <mergeCell ref="B94:B101"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C136:C138"/>
-    <mergeCell ref="B113:B115"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="C142:C143"/>
     <mergeCell ref="B73:B76"/>
-    <mergeCell ref="D113:D115"/>
     <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="B114:B120"/>
     <mergeCell ref="V5:AB5"/>
     <mergeCell ref="B41:B58"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="B146:B149"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="A121:A131"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B106:B112"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="C155:C156"/>
     <mergeCell ref="B9:B14"/>
     <mergeCell ref="W4:AZ4"/>
     <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C161:C162"/>
     <mergeCell ref="B33:B40"/>
-    <mergeCell ref="D110:D111"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="D128:D129"/>
     <mergeCell ref="AQ5:AW5"/>
-    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="C148:C150"/>
+    <mergeCell ref="B147:B153"/>
     <mergeCell ref="G2:Z2"/>
-    <mergeCell ref="D120:D121"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="C140:C142"/>
+    <mergeCell ref="D114:D116"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="B142:B146"/>
+    <mergeCell ref="C124:C127"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="B77:B88"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="C130:C133"/>
-    <mergeCell ref="B134:B138"/>
+    <mergeCell ref="D148:D149"/>
+    <mergeCell ref="B103:B110"/>
     <mergeCell ref="B15:B20"/>
+    <mergeCell ref="B132:B141"/>
+    <mergeCell ref="C158:C159"/>
+    <mergeCell ref="D132:D133"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="B154:B157"/>
     <mergeCell ref="G1:N1"/>
     <mergeCell ref="BE5:BG5"/>
     <mergeCell ref="B89:B92"/>
-    <mergeCell ref="C147:C148"/>
     <mergeCell ref="D124:D125"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
